--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -57504,6 +57504,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2485">
+      <c r="A2485" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2485" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2485" t="n">
+        <v>54</v>
+      </c>
+      <c r="D2485" t="n">
+        <v>54</v>
+      </c>
+      <c r="E2485" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2485" t="n">
+        <v>54</v>
+      </c>
+      <c r="G2485" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2486" t="n">
+        <v>750</v>
+      </c>
+      <c r="C2486" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D2486" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="E2486" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="F2486" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="G2486" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -57550,6 +57550,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2487">
+      <c r="A2487" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2487" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2487" t="n">
+        <v>56</v>
+      </c>
+      <c r="D2487" t="n">
+        <v>55</v>
+      </c>
+      <c r="E2487" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2487" t="n">
+        <v>56</v>
+      </c>
+      <c r="G2487" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -57573,6 +57573,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>4250</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>57</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -57414,22 +57414,22 @@
     </row>
     <row r="2481">
       <c r="A2481" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2481" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="C2481" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2481" t="n">
         <v>53.5</v>
       </c>
       <c r="E2481" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="F2481" t="n">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="G2481" t="s">
         <v>7</v>
@@ -57437,19 +57437,19 @@
     </row>
     <row r="2482">
       <c r="A2482" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2482" t="n">
-        <v>250</v>
+        <v>3500</v>
       </c>
       <c r="C2482" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="D2482" t="n">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="E2482" t="n">
-        <v>54.5</v>
+        <v>54</v>
       </c>
       <c r="F2482" t="n">
         <v>54.5</v>
@@ -57460,10 +57460,10 @@
     </row>
     <row r="2483">
       <c r="A2483" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2483" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C2483" t="n">
         <v>54.5</v>
@@ -57483,22 +57483,22 @@
     </row>
     <row r="2484">
       <c r="A2484" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2484" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="C2484" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="D2484" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="E2484" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="F2484" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="G2484" t="s">
         <v>7</v>
@@ -57506,19 +57506,19 @@
     </row>
     <row r="2485">
       <c r="A2485" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2485" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="C2485" t="n">
         <v>54</v>
       </c>
       <c r="D2485" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="E2485" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="F2485" t="n">
         <v>54</v>
@@ -57529,22 +57529,22 @@
     </row>
     <row r="2486">
       <c r="A2486" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2486" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="C2486" t="n">
-        <v>54.5</v>
+        <v>54</v>
       </c>
       <c r="D2486" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="E2486" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="F2486" t="n">
-        <v>54.5</v>
+        <v>54</v>
       </c>
       <c r="G2486" t="s">
         <v>7</v>
@@ -57552,22 +57552,22 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2487" t="n">
-        <v>3000</v>
+        <v>750</v>
       </c>
       <c r="C2487" t="n">
-        <v>56</v>
+        <v>54.5</v>
       </c>
       <c r="D2487" t="n">
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="E2487" t="n">
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="F2487" t="n">
-        <v>56</v>
+        <v>54.5</v>
       </c>
       <c r="G2487" t="s">
         <v>7</v>
@@ -57575,24 +57575,47 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2488" t="n">
-        <v>4250</v>
+        <v>3000</v>
       </c>
       <c r="C2488" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2488" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="E2488" t="n">
         <v>55</v>
       </c>
       <c r="F2488" t="n">
+        <v>56</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>250</v>
+      </c>
+      <c r="C2489" t="n">
         <v>56.5</v>
       </c>
-      <c r="G2488" t="s">
+      <c r="D2489" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G2489" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -57888,8 +57888,31 @@
       <c r="E2501" t="n">
         <v>56</v>
       </c>
-      <c r="F2501"/>
+      <c r="F2501" t="n">
+        <v>56</v>
+      </c>
       <c r="G2501" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>6250</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>56</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2502"/>
+      <c r="G2502" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -57911,8 +57911,31 @@
       <c r="E2502" t="n">
         <v>56</v>
       </c>
-      <c r="F2502"/>
+      <c r="F2502" t="n">
+        <v>58.5</v>
+      </c>
       <c r="G2502" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2503"/>
+      <c r="G2503" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -57934,8 +57934,31 @@
       <c r="E2503" t="n">
         <v>58</v>
       </c>
-      <c r="F2503"/>
+      <c r="F2503" t="n">
+        <v>58</v>
+      </c>
       <c r="G2503" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>58</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2504"/>
+      <c r="G2504" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -57957,8 +57957,31 @@
       <c r="E2504" t="n">
         <v>58</v>
       </c>
-      <c r="F2504"/>
+      <c r="F2504" t="n">
+        <v>60</v>
+      </c>
       <c r="G2504" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>59</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2505"/>
+      <c r="G2505" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -57987,6 +57987,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.39585494995117</v>
+        <v>2.39585518836975</v>
       </c>
       <c r="H2" t="n">
         <v>9000</v>
@@ -456,7 +456,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.39585494995117</v>
+        <v>2.39585518836975</v>
       </c>
       <c r="H3" t="n">
         <v>1000</v>
@@ -485,7 +485,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>2.35782599449158</v>
+        <v>2.35782527923584</v>
       </c>
       <c r="H4" t="n">
         <v>500</v>
@@ -514,7 +514,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G5" t="n">
-        <v>2.36543083190918</v>
+        <v>2.36543154716492</v>
       </c>
       <c r="H5" t="n">
         <v>500</v>
@@ -717,7 +717,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>2.35782599449158</v>
+        <v>2.35782527923584</v>
       </c>
       <c r="H12" t="n">
         <v>1000</v>
@@ -746,7 +746,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>2.35782599449158</v>
+        <v>2.35782527923584</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>2.35782599449158</v>
+        <v>2.35782527923584</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
@@ -804,7 +804,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32740163803101</v>
+        <v>2.32740211486816</v>
       </c>
       <c r="H15" t="n">
         <v>1500</v>
@@ -833,7 +833,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.32740163803101</v>
+        <v>2.32740211486816</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>2.32740163803101</v>
+        <v>2.32740211486816</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>2.26655507087708</v>
+        <v>2.2665548324585</v>
       </c>
       <c r="H18" t="n">
         <v>1500</v>
@@ -920,7 +920,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>2.26655507087708</v>
+        <v>2.2665548324585</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G20" t="n">
-        <v>2.26655507087708</v>
+        <v>2.2665548324585</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.26655507087708</v>
+        <v>2.2665548324585</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G22" t="n">
-        <v>2.26655507087708</v>
+        <v>2.2665548324585</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>2.26655507087708</v>
+        <v>2.2665548324585</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>2.26655507087708</v>
+        <v>2.2665548324585</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>2.26655507087708</v>
+        <v>2.2665548324585</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G26" t="n">
-        <v>2.26655507087708</v>
+        <v>2.2665548324585</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G27" t="n">
-        <v>2.35021948814392</v>
+        <v>2.3502197265625</v>
       </c>
       <c r="H27" t="n">
         <v>6000</v>
@@ -1181,7 +1181,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G28" t="n">
-        <v>2.35021948814392</v>
+        <v>2.3502197265625</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28937244415283</v>
+        <v>2.28937268257141</v>
       </c>
       <c r="H29" t="n">
         <v>1000</v>
@@ -1239,7 +1239,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G30" t="n">
-        <v>2.28937244415283</v>
+        <v>2.28937268257141</v>
       </c>
       <c r="H30" t="n">
         <v>1500</v>
@@ -1268,7 +1268,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G31" t="n">
-        <v>2.28937244415283</v>
+        <v>2.28937268257141</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G32" t="n">
-        <v>2.28937244415283</v>
+        <v>2.28937268257141</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G33" t="n">
-        <v>2.28937244415283</v>
+        <v>2.28937268257141</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G38" t="n">
-        <v>2.32740163803101</v>
+        <v>2.32740211486816</v>
       </c>
       <c r="H38" t="n">
         <v>2000</v>
@@ -1558,7 +1558,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.43388438224792</v>
+        <v>2.4338846206665</v>
       </c>
       <c r="H41" t="n">
         <v>10000</v>
@@ -1587,7 +1587,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G42" t="n">
-        <v>2.35782599449158</v>
+        <v>2.35782527923584</v>
       </c>
       <c r="H42" t="n">
         <v>3500</v>
@@ -1616,7 +1616,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H43" t="n">
         <v>1000</v>
@@ -1645,7 +1645,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G44" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H44" t="n">
         <v>1000</v>
@@ -1674,7 +1674,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.38064336776733</v>
+        <v>2.38064312934875</v>
       </c>
       <c r="H55" t="n">
         <v>5000</v>
@@ -1993,7 +1993,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G56" t="n">
-        <v>2.3061056137085</v>
+        <v>2.30610513687134</v>
       </c>
       <c r="H56" t="n">
         <v>1000</v>
@@ -2022,7 +2022,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G57" t="n">
-        <v>2.3061056137085</v>
+        <v>2.30610513687134</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G58" t="n">
-        <v>2.3061056137085</v>
+        <v>2.30610513687134</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G59" t="n">
-        <v>2.28328824043274</v>
+        <v>2.28328776359558</v>
       </c>
       <c r="H59" t="n">
         <v>1500</v>
@@ -2109,7 +2109,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G60" t="n">
-        <v>2.28328824043274</v>
+        <v>2.28328776359558</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>2.31979608535767</v>
+        <v>2.31979632377625</v>
       </c>
       <c r="H62" t="n">
         <v>4500</v>
@@ -2196,7 +2196,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G63" t="n">
-        <v>2.31979608535767</v>
+        <v>2.31979632377625</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>2.31979608535767</v>
+        <v>2.31979632377625</v>
       </c>
       <c r="H65" t="n">
         <v>500</v>
@@ -2283,7 +2283,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G66" t="n">
-        <v>2.31979608535767</v>
+        <v>2.31979632377625</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>2.31979608535767</v>
+        <v>2.31979632377625</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>2.31979608535767</v>
+        <v>2.31979632377625</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G69" t="n">
-        <v>2.38520693778992</v>
+        <v>2.38520669937134</v>
       </c>
       <c r="H69" t="n">
         <v>1000</v>
@@ -2399,7 +2399,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G70" t="n">
-        <v>2.32740163803101</v>
+        <v>2.32740211486816</v>
       </c>
       <c r="H70" t="n">
         <v>1000</v>
@@ -2428,7 +2428,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.32740163803101</v>
+        <v>2.32740211486816</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>2.32740163803101</v>
+        <v>2.32740211486816</v>
       </c>
       <c r="H72" t="n">
         <v>500</v>
@@ -2544,7 +2544,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.31979608535767</v>
+        <v>2.31979632377625</v>
       </c>
       <c r="H75" t="n">
         <v>8500</v>
@@ -2573,7 +2573,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H76" t="n">
         <v>3000</v>
@@ -2602,7 +2602,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G77" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G79" t="n">
-        <v>2.38064336776733</v>
+        <v>2.38064312934875</v>
       </c>
       <c r="H79" t="n">
         <v>7000</v>
@@ -2689,7 +2689,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G80" t="n">
-        <v>2.29697871208191</v>
+        <v>2.29697823524475</v>
       </c>
       <c r="H80" t="n">
         <v>4500</v>
@@ -2776,7 +2776,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G83" t="n">
-        <v>2.31219029426575</v>
+        <v>2.31219005584717</v>
       </c>
       <c r="H83" t="n">
         <v>3000</v>
@@ -2805,7 +2805,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>2.31219029426575</v>
+        <v>2.31219005584717</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>2.31219029426575</v>
+        <v>2.31219005584717</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G87" t="n">
-        <v>2.318274974823</v>
+        <v>2.31827521324158</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2921,7 +2921,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G88" t="n">
-        <v>2.318274974823</v>
+        <v>2.31827521324158</v>
       </c>
       <c r="H88" t="n">
         <v>500</v>
@@ -2950,7 +2950,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G89" t="n">
-        <v>2.318274974823</v>
+        <v>2.31827521324158</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G90" t="n">
-        <v>2.318274974823</v>
+        <v>2.31827521324158</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3008,7 +3008,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>2.37303733825684</v>
+        <v>2.37303709983826</v>
       </c>
       <c r="H91" t="n">
         <v>12500</v>
@@ -3037,7 +3037,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G92" t="n">
-        <v>2.70161151885986</v>
+        <v>2.70161175727844</v>
       </c>
       <c r="H92" t="n">
         <v>11500</v>
@@ -3066,7 +3066,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G93" t="n">
-        <v>3.27205324172974</v>
+        <v>3.27205348014832</v>
       </c>
       <c r="H93" t="n">
         <v>21500</v>
@@ -3095,7 +3095,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G94" t="n">
-        <v>3.52304816246033</v>
+        <v>3.52304768562317</v>
       </c>
       <c r="H94" t="n">
         <v>42500</v>
@@ -3124,7 +3124,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>3.21729111671448</v>
+        <v>3.21729063987732</v>
       </c>
       <c r="H95" t="n">
         <v>26500</v>
@@ -3153,7 +3153,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G96" t="n">
-        <v>3.16404938697815</v>
+        <v>3.16404986381531</v>
       </c>
       <c r="H96" t="n">
         <v>7000</v>
@@ -3182,7 +3182,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11232972145081</v>
+        <v>3.11232948303223</v>
       </c>
       <c r="H97" t="n">
         <v>4500</v>
@@ -3211,7 +3211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>2.96629643440247</v>
+        <v>2.96629667282104</v>
       </c>
       <c r="H98" t="n">
         <v>11000</v>
@@ -3269,7 +3269,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.95869088172913</v>
+        <v>2.95869064331055</v>
       </c>
       <c r="H100" t="n">
         <v>2000</v>
@@ -3298,7 +3298,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.95108461380005</v>
+        <v>2.95108485221863</v>
       </c>
       <c r="H101" t="n">
         <v>500</v>
@@ -3327,7 +3327,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G102" t="n">
-        <v>2.95260620117188</v>
+        <v>2.9526059627533</v>
       </c>
       <c r="H102" t="n">
         <v>3000</v>
@@ -3414,7 +3414,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G105" t="n">
-        <v>3.20968461036682</v>
+        <v>3.2096848487854</v>
       </c>
       <c r="H105" t="n">
         <v>7000</v>
@@ -3472,7 +3472,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G107" t="n">
-        <v>3.47589135169983</v>
+        <v>3.47589159011841</v>
       </c>
       <c r="H107" t="n">
         <v>10500</v>
@@ -3559,7 +3559,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>3.30856132507324</v>
+        <v>3.30856204032898</v>
       </c>
       <c r="H110" t="n">
         <v>9500</v>
@@ -3588,7 +3588,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.49110269546509</v>
+        <v>3.49110317230225</v>
       </c>
       <c r="H111" t="n">
         <v>5500</v>
@@ -3617,7 +3617,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.48349714279175</v>
+        <v>3.48349690437317</v>
       </c>
       <c r="H112" t="n">
         <v>9500</v>
@@ -3675,7 +3675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.49870824813843</v>
+        <v>3.49870848655701</v>
       </c>
       <c r="H114" t="n">
         <v>6000</v>
@@ -3704,7 +3704,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G115" t="n">
-        <v>3.49870824813843</v>
+        <v>3.49870848655701</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G119" t="n">
-        <v>3.27205324172974</v>
+        <v>3.27205348014832</v>
       </c>
       <c r="H119" t="n">
         <v>1000</v>
@@ -3936,7 +3936,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>3.30856132507324</v>
+        <v>3.30856204032898</v>
       </c>
       <c r="H123" t="n">
         <v>2500</v>
@@ -3965,7 +3965,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G124" t="n">
-        <v>3.28726506233215</v>
+        <v>3.28726482391357</v>
       </c>
       <c r="H124" t="n">
         <v>1500</v>
@@ -3994,7 +3994,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>3.34659171104431</v>
+        <v>3.34659099578857</v>
       </c>
       <c r="H125" t="n">
         <v>4500</v>
@@ -4110,7 +4110,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G129" t="n">
-        <v>3.48958206176758</v>
+        <v>3.489581823349</v>
       </c>
       <c r="H129" t="n">
         <v>500</v>
@@ -4139,7 +4139,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>3.49110269546509</v>
+        <v>3.49110317230225</v>
       </c>
       <c r="H130" t="n">
         <v>500</v>
@@ -4284,7 +4284,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G135" t="n">
-        <v>3.31616711616516</v>
+        <v>3.31616759300232</v>
       </c>
       <c r="H135" t="n">
         <v>4500</v>
@@ -4313,7 +4313,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G136" t="n">
-        <v>3.14883756637573</v>
+        <v>3.14883804321289</v>
       </c>
       <c r="H136" t="n">
         <v>1500</v>
@@ -4342,7 +4342,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>3.1199357509613</v>
+        <v>3.11993598937988</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4400,7 +4400,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>3.30856132507324</v>
+        <v>3.30856204032898</v>
       </c>
       <c r="H139" t="n">
         <v>2500</v>
@@ -4429,7 +4429,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>3.30856132507324</v>
+        <v>3.30856204032898</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>3.30856132507324</v>
+        <v>3.30856204032898</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>3.11841440200806</v>
+        <v>3.11841416358948</v>
       </c>
       <c r="H143" t="n">
         <v>2500</v>
@@ -4545,7 +4545,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>3.11841440200806</v>
+        <v>3.11841416358948</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>3.04996204376221</v>
+        <v>3.04996156692505</v>
       </c>
       <c r="H145" t="n">
         <v>500</v>
@@ -4603,7 +4603,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>3.14123225212097</v>
+        <v>3.14123249053955</v>
       </c>
       <c r="H146" t="n">
         <v>1000</v>
@@ -4632,7 +4632,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>3.14123225212097</v>
+        <v>3.14123249053955</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.22489643096924</v>
+        <v>3.22489666938782</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>3.22489643096924</v>
+        <v>3.22489666938782</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G150" t="n">
-        <v>3.22489643096924</v>
+        <v>3.22489666938782</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G151" t="n">
-        <v>3.22489643096924</v>
+        <v>3.22489666938782</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G152" t="n">
-        <v>3.22489643096924</v>
+        <v>3.22489666938782</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G153" t="n">
-        <v>3.22489643096924</v>
+        <v>3.22489666938782</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>3.22489643096924</v>
+        <v>3.22489666938782</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G155" t="n">
-        <v>3.18382501602173</v>
+        <v>3.18382525444031</v>
       </c>
       <c r="H155" t="n">
         <v>3000</v>
@@ -4922,7 +4922,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G157" t="n">
-        <v>3.05452466011047</v>
+        <v>3.05452489852905</v>
       </c>
       <c r="H157" t="n">
         <v>500</v>
@@ -4951,7 +4951,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G158" t="n">
-        <v>3.02714395523071</v>
+        <v>3.02714371681213</v>
       </c>
       <c r="H158" t="n">
         <v>9000</v>
@@ -4980,7 +4980,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>2.95108461380005</v>
+        <v>2.95108485221863</v>
       </c>
       <c r="H159" t="n">
         <v>1000</v>
@@ -5009,7 +5009,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G160" t="n">
-        <v>2.95108461380005</v>
+        <v>2.95108485221863</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G161" t="n">
-        <v>2.91609787940979</v>
+        <v>2.91609764099121</v>
       </c>
       <c r="H161" t="n">
         <v>1000</v>
@@ -5067,7 +5067,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G162" t="n">
-        <v>2.91609787940979</v>
+        <v>2.91609764099121</v>
       </c>
       <c r="H162" t="n">
         <v>3000</v>
@@ -5154,7 +5154,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G165" t="n">
-        <v>2.97390270233154</v>
+        <v>2.97390222549438</v>
       </c>
       <c r="H165" t="n">
         <v>1000</v>
@@ -5183,7 +5183,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>2.97390270233154</v>
+        <v>2.97390222549438</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.82178449630737</v>
+        <v>2.82178473472595</v>
       </c>
       <c r="H167" t="n">
         <v>4000</v>
@@ -5241,7 +5241,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.81417918205261</v>
+        <v>2.81417894363403</v>
       </c>
       <c r="H168" t="n">
         <v>4000</v>
@@ -5270,7 +5270,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>2.81417918205261</v>
+        <v>2.81417894363403</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G170" t="n">
-        <v>2.74876832962036</v>
+        <v>2.74876809120178</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5328,7 +5328,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G171" t="n">
-        <v>2.74876832962036</v>
+        <v>2.74876809120178</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G172" t="n">
-        <v>2.74876832962036</v>
+        <v>2.74876809120178</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G173" t="n">
-        <v>2.81417918205261</v>
+        <v>2.81417894363403</v>
       </c>
       <c r="H173" t="n">
         <v>1000</v>
@@ -5415,7 +5415,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G174" t="n">
-        <v>2.81417918205261</v>
+        <v>2.81417894363403</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>2.82178449630737</v>
+        <v>2.82178473472595</v>
       </c>
       <c r="H176" t="n">
         <v>500</v>
@@ -5502,7 +5502,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>2.82178449630737</v>
+        <v>2.82178473472595</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>2.82178449630737</v>
+        <v>2.82178473472595</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>2.96629643440247</v>
+        <v>2.96629667282104</v>
       </c>
       <c r="H179" t="n">
         <v>2000</v>
@@ -5589,7 +5589,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>2.96629643440247</v>
+        <v>2.96629667282104</v>
       </c>
       <c r="H180" t="n">
         <v>3000</v>
@@ -5676,7 +5676,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G183" t="n">
-        <v>2.97846579551697</v>
+        <v>2.97846603393555</v>
       </c>
       <c r="H183" t="n">
         <v>1500</v>
@@ -5705,7 +5705,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G184" t="n">
-        <v>2.97846579551697</v>
+        <v>2.97846603393555</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G185" t="n">
-        <v>2.97846579551697</v>
+        <v>2.97846603393555</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G186" t="n">
-        <v>2.97846579551697</v>
+        <v>2.97846603393555</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G191" t="n">
-        <v>2.97390270233154</v>
+        <v>2.97390222549438</v>
       </c>
       <c r="H191" t="n">
         <v>500</v>
@@ -5937,7 +5937,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G192" t="n">
-        <v>2.97390270233154</v>
+        <v>2.97390222549438</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G193" t="n">
-        <v>2.97390270233154</v>
+        <v>2.97390222549438</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G194" t="n">
-        <v>2.97390270233154</v>
+        <v>2.97390222549438</v>
       </c>
       <c r="H194" t="n">
         <v>6500</v>
@@ -6024,7 +6024,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G195" t="n">
-        <v>2.97390270233154</v>
+        <v>2.97390222549438</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G198" t="n">
-        <v>3.12297773361206</v>
+        <v>3.12297749519348</v>
       </c>
       <c r="H198" t="n">
         <v>500</v>
@@ -6140,7 +6140,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G199" t="n">
-        <v>3.19295191764832</v>
+        <v>3.19295215606689</v>
       </c>
       <c r="H199" t="n">
         <v>500</v>
@@ -6169,7 +6169,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>3.19295191764832</v>
+        <v>3.19295215606689</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G201" t="n">
-        <v>3.19295191764832</v>
+        <v>3.19295215606689</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G202" t="n">
-        <v>3.2644476890564</v>
+        <v>3.26444697380066</v>
       </c>
       <c r="H202" t="n">
         <v>1000</v>
@@ -6343,7 +6343,7 @@
         <v>5</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80294418334961</v>
+        <v>3.80294394493103</v>
       </c>
       <c r="H206" t="n">
         <v>40000</v>
@@ -6517,7 +6517,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>5.5522985458374</v>
+        <v>5.55229949951172</v>
       </c>
       <c r="H212" t="n">
         <v>43500</v>
@@ -6546,7 +6546,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G213" t="n">
-        <v>5.41158962249756</v>
+        <v>5.41159009933472</v>
       </c>
       <c r="H213" t="n">
         <v>30500</v>
@@ -6575,7 +6575,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>5.26707792282104</v>
+        <v>5.26707744598389</v>
       </c>
       <c r="H214" t="n">
         <v>9500</v>
@@ -6633,7 +6633,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G216" t="n">
-        <v>4.80692148208618</v>
+        <v>4.80692195892334</v>
       </c>
       <c r="H216" t="n">
         <v>7000</v>
@@ -6662,7 +6662,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G217" t="n">
-        <v>4.57113933563232</v>
+        <v>4.57113981246948</v>
       </c>
       <c r="H217" t="n">
         <v>8000</v>
@@ -6691,7 +6691,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>4.544517993927</v>
+        <v>4.54451942443848</v>
       </c>
       <c r="H218" t="n">
         <v>2500</v>
@@ -6720,7 +6720,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>4.86776876449585</v>
+        <v>4.86776924133301</v>
       </c>
       <c r="H219" t="n">
         <v>7500</v>
@@ -6749,7 +6749,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G220" t="n">
-        <v>5.40018129348755</v>
+        <v>5.40018081665039</v>
       </c>
       <c r="H220" t="n">
         <v>31500</v>
@@ -6778,7 +6778,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G221" t="n">
-        <v>5.15679359436035</v>
+        <v>5.15679264068604</v>
       </c>
       <c r="H221" t="n">
         <v>15000</v>
@@ -6807,7 +6807,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G222" t="n">
-        <v>5.07693147659302</v>
+        <v>5.07693099975586</v>
       </c>
       <c r="H222" t="n">
         <v>9500</v>
@@ -6836,7 +6836,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G223" t="n">
-        <v>5.0503101348877</v>
+        <v>5.05030965805054</v>
       </c>
       <c r="H223" t="n">
         <v>1500</v>
@@ -6894,7 +6894,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G225" t="n">
-        <v>5.31651592254639</v>
+        <v>5.31651639938354</v>
       </c>
       <c r="H225" t="n">
         <v>4500</v>
@@ -6923,7 +6923,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>5.40018129348755</v>
+        <v>5.40018081665039</v>
       </c>
       <c r="H226" t="n">
         <v>4000</v>
@@ -6952,7 +6952,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G227" t="n">
-        <v>5.2176399230957</v>
+        <v>5.21763944625854</v>
       </c>
       <c r="H227" t="n">
         <v>2500</v>
@@ -6981,7 +6981,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G228" t="n">
-        <v>5.1415810585022</v>
+        <v>5.14158058166504</v>
       </c>
       <c r="H228" t="n">
         <v>3000</v>
@@ -7010,7 +7010,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G229" t="n">
-        <v>5.02749300003052</v>
+        <v>5.02749252319336</v>
       </c>
       <c r="H229" t="n">
         <v>1500</v>
@@ -7039,7 +7039,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G230" t="n">
-        <v>5.02749300003052</v>
+        <v>5.02749252319336</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G232" t="n">
-        <v>5.07312822341919</v>
+        <v>5.07312774658203</v>
       </c>
       <c r="H232" t="n">
         <v>1000</v>
@@ -7126,7 +7126,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>5.07312822341919</v>
+        <v>5.07312774658203</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>5.00847768783569</v>
+        <v>5.00847816467285</v>
       </c>
       <c r="H238" t="n">
         <v>4500</v>
@@ -7416,7 +7416,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>4.62438058853149</v>
+        <v>4.62438011169434</v>
       </c>
       <c r="H243" t="n">
         <v>4000</v>
@@ -7503,7 +7503,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G246" t="n">
-        <v>4.74987697601318</v>
+        <v>4.74987745285034</v>
       </c>
       <c r="H246" t="n">
         <v>500</v>
@@ -7532,7 +7532,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.69663572311401</v>
+        <v>4.69663667678833</v>
       </c>
       <c r="H247" t="n">
         <v>2500</v>
@@ -7561,7 +7561,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.69663572311401</v>
+        <v>4.69663667678833</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>4.62057733535767</v>
+        <v>4.62057781219482</v>
       </c>
       <c r="H249" t="n">
         <v>500</v>
@@ -7648,7 +7648,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G251" t="n">
-        <v>4.59015417098999</v>
+        <v>4.59015369415283</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -7677,7 +7677,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G252" t="n">
-        <v>4.59015417098999</v>
+        <v>4.59015369415283</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G255" t="n">
-        <v>4.64719772338867</v>
+        <v>4.64719867706299</v>
       </c>
       <c r="H255" t="n">
         <v>2500</v>
@@ -7793,7 +7793,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G256" t="n">
-        <v>4.73846864700317</v>
+        <v>4.73846817016602</v>
       </c>
       <c r="H256" t="n">
         <v>4000</v>
@@ -7822,7 +7822,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>4.89439010620117</v>
+        <v>4.89438915252686</v>
       </c>
       <c r="H257" t="n">
         <v>1000</v>
@@ -7880,7 +7880,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>4.67762136459351</v>
+        <v>4.67762184143066</v>
       </c>
       <c r="H259" t="n">
         <v>1500</v>
@@ -7996,7 +7996,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G263" t="n">
-        <v>4.86016273498535</v>
+        <v>4.86016178131104</v>
       </c>
       <c r="H263" t="n">
         <v>1500</v>
@@ -8054,7 +8054,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G265" t="n">
-        <v>4.63959217071533</v>
+        <v>4.63959264755249</v>
       </c>
       <c r="H265" t="n">
         <v>3000</v>
@@ -8083,7 +8083,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G266" t="n">
-        <v>4.63959217071533</v>
+        <v>4.63959264755249</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>4.67762136459351</v>
+        <v>4.67762184143066</v>
       </c>
       <c r="H267" t="n">
         <v>500</v>
@@ -8141,7 +8141,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>4.67762136459351</v>
+        <v>4.67762184143066</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>4.5673360824585</v>
+        <v>4.56733655929565</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G273" t="n">
-        <v>4.5673360824585</v>
+        <v>4.56733655929565</v>
       </c>
       <c r="H273" t="n">
         <v>500</v>
@@ -8373,7 +8373,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>4.76889276504517</v>
+        <v>4.76889228820801</v>
       </c>
       <c r="H276" t="n">
         <v>2500</v>
@@ -8402,7 +8402,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>4.76889276504517</v>
+        <v>4.76889228820801</v>
       </c>
       <c r="H277" t="n">
         <v>2500</v>
@@ -8489,7 +8489,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>5.28609275817871</v>
+        <v>5.28609323501587</v>
       </c>
       <c r="H280" t="n">
         <v>9500</v>
@@ -8634,7 +8634,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G285" t="n">
-        <v>5.09594488143921</v>
+        <v>5.09594583511353</v>
       </c>
       <c r="H285" t="n">
         <v>500</v>
@@ -8692,7 +8692,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G287" t="n">
-        <v>5.24806356430054</v>
+        <v>5.24806308746338</v>
       </c>
       <c r="H287" t="n">
         <v>11500</v>
@@ -8721,7 +8721,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.24806356430054</v>
+        <v>5.24806308746338</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8779,7 +8779,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G290" t="n">
-        <v>5.36215162277222</v>
+        <v>5.36215114593506</v>
       </c>
       <c r="H290" t="n">
         <v>23500</v>
@@ -8808,7 +8808,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.47624015808105</v>
+        <v>5.4762396812439</v>
       </c>
       <c r="H291" t="n">
         <v>7000</v>
@@ -8837,7 +8837,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.40018129348755</v>
+        <v>5.40018081665039</v>
       </c>
       <c r="H292" t="n">
         <v>16000</v>
@@ -8866,7 +8866,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.40018129348755</v>
+        <v>5.40018081665039</v>
       </c>
       <c r="H293" t="n">
         <v>4500</v>
@@ -8953,7 +8953,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.24806356430054</v>
+        <v>5.24806308746338</v>
       </c>
       <c r="H296" t="n">
         <v>2500</v>
@@ -8982,7 +8982,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>5.24806356430054</v>
+        <v>5.24806308746338</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G298" t="n">
-        <v>5.09594488143921</v>
+        <v>5.09594583511353</v>
       </c>
       <c r="H298" t="n">
         <v>7500</v>
@@ -9040,7 +9040,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>5.09594488143921</v>
+        <v>5.09594583511353</v>
       </c>
       <c r="H299" t="n">
         <v>1500</v>
@@ -9127,7 +9127,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>4.82973909378052</v>
+        <v>4.82973957061768</v>
       </c>
       <c r="H302" t="n">
         <v>2000</v>
@@ -9156,7 +9156,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G303" t="n">
-        <v>4.79170989990234</v>
+        <v>4.7917103767395</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9185,7 +9185,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>4.86776876449585</v>
+        <v>4.86776924133301</v>
       </c>
       <c r="H304" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>4.86776876449585</v>
+        <v>4.86776924133301</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>4.79170989990234</v>
+        <v>4.7917103767395</v>
       </c>
       <c r="H306" t="n">
         <v>3000</v>
@@ -9272,7 +9272,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>4.79170989990234</v>
+        <v>4.7917103767395</v>
       </c>
       <c r="H307" t="n">
         <v>1000</v>
@@ -9301,7 +9301,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G308" t="n">
-        <v>4.79170989990234</v>
+        <v>4.7917103767395</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>4.79170989990234</v>
+        <v>4.7917103767395</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>4.79170989990234</v>
+        <v>4.7917103767395</v>
       </c>
       <c r="H310" t="n">
         <v>2000</v>
@@ -9388,7 +9388,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.71565198898315</v>
+        <v>4.71565055847168</v>
       </c>
       <c r="H311" t="n">
         <v>1000</v>
@@ -9417,7 +9417,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>4.71565198898315</v>
+        <v>4.71565055847168</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98185729980469</v>
+        <v>4.98185777664185</v>
       </c>
       <c r="H313" t="n">
         <v>2500</v>
@@ -9591,7 +9591,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G318" t="n">
-        <v>5.09594488143921</v>
+        <v>5.09594583511353</v>
       </c>
       <c r="H318" t="n">
         <v>1500</v>
@@ -9620,7 +9620,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>4.98185729980469</v>
+        <v>4.98185777664185</v>
       </c>
       <c r="H319" t="n">
         <v>500</v>
@@ -9649,7 +9649,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>4.98185729980469</v>
+        <v>4.98185777664185</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>4.71565198898315</v>
+        <v>4.71565055847168</v>
       </c>
       <c r="H322" t="n">
         <v>1500</v>
@@ -9968,7 +9968,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.28609275817871</v>
+        <v>5.28609323501587</v>
       </c>
       <c r="H331" t="n">
         <v>2500</v>
@@ -10113,7 +10113,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>5.24806356430054</v>
+        <v>5.24806308746338</v>
       </c>
       <c r="H336" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>5.24806356430054</v>
+        <v>5.24806308746338</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>5.43821096420288</v>
+        <v>5.43821048736572</v>
       </c>
       <c r="H341" t="n">
         <v>8500</v>
@@ -10345,7 +10345,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>5.43821096420288</v>
+        <v>5.43821048736572</v>
       </c>
       <c r="H344" t="n">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.43821096420288</v>
+        <v>5.43821048736572</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>5.40018129348755</v>
+        <v>5.40018081665039</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>5.40018129348755</v>
+        <v>5.40018081665039</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G348" t="n">
-        <v>5.36215162277222</v>
+        <v>5.36215114593506</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10519,7 +10519,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G350" t="n">
-        <v>5.28609275817871</v>
+        <v>5.28609323501587</v>
       </c>
       <c r="H350" t="n">
         <v>500</v>
@@ -10548,7 +10548,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G351" t="n">
-        <v>5.36215162277222</v>
+        <v>5.36215114593506</v>
       </c>
       <c r="H351" t="n">
         <v>1500</v>
@@ -10722,7 +10722,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.24806356430054</v>
+        <v>5.24806308746338</v>
       </c>
       <c r="H357" t="n">
         <v>1000</v>
@@ -10751,7 +10751,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.24806356430054</v>
+        <v>5.24806308746338</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H367" t="n">
         <v>1500</v>
@@ -11041,7 +11041,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H368" t="n">
         <v>500</v>
@@ -11070,7 +11070,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G370" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G371" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G372" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G374" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H374" t="n">
         <v>1000</v>
@@ -11244,7 +11244,7 @@
         <v>6.5</v>
       </c>
       <c r="G375" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H375" t="n">
         <v>500</v>
@@ -11273,7 +11273,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G376" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H376" t="n">
         <v>500</v>
@@ -11302,7 +11302,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H377" t="n">
         <v>500</v>
@@ -11331,7 +11331,7 @@
         <v>6.75</v>
       </c>
       <c r="G378" t="n">
-        <v>5.2294020652771</v>
+        <v>5.22940254211426</v>
       </c>
       <c r="H378" t="n">
         <v>4000</v>
@@ -11389,7 +11389,7 @@
         <v>6.5</v>
       </c>
       <c r="G380" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>6.5</v>
       </c>
       <c r="G381" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>6.5</v>
       </c>
       <c r="G382" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>6.5</v>
       </c>
       <c r="G383" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>6.5</v>
       </c>
       <c r="G384" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.5</v>
       </c>
       <c r="G385" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H385" t="n">
         <v>500</v>
@@ -11563,7 +11563,7 @@
         <v>6.5</v>
       </c>
       <c r="G386" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>6.5</v>
       </c>
       <c r="G387" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H387" t="n">
         <v>500</v>
@@ -11621,7 +11621,7 @@
         <v>6.5</v>
       </c>
       <c r="G388" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>6.5</v>
       </c>
       <c r="G389" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H390" t="n">
         <v>2500</v>
@@ -11708,7 +11708,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H391" t="n">
         <v>500</v>
@@ -11766,7 +11766,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H393" t="n">
         <v>1000</v>
@@ -11795,7 +11795,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H394" t="n">
         <v>500</v>
@@ -11824,7 +11824,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H396" t="n">
         <v>500</v>
@@ -11882,7 +11882,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G397" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G398" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>6.5</v>
       </c>
       <c r="G399" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H399" t="n">
         <v>1000</v>
@@ -11969,7 +11969,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>4.76456594467163</v>
+        <v>4.76456642150879</v>
       </c>
       <c r="H400" t="n">
         <v>1000</v>
@@ -11998,7 +11998,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H401" t="n">
         <v>500</v>
@@ -12027,7 +12027,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G402" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H402" t="n">
         <v>500</v>
@@ -12056,7 +12056,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G403" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G404" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.34561157226562</v>
+        <v>5.34561061859131</v>
       </c>
       <c r="H405" t="n">
         <v>9000</v>
@@ -12143,7 +12143,7 @@
         <v>6.75</v>
       </c>
       <c r="G406" t="n">
-        <v>5.2294020652771</v>
+        <v>5.22940254211426</v>
       </c>
       <c r="H406" t="n">
         <v>500</v>
@@ -12172,7 +12172,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>5.30687475204468</v>
+        <v>5.30687522888184</v>
       </c>
       <c r="H407" t="n">
         <v>1500</v>
@@ -12201,7 +12201,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.34561157226562</v>
+        <v>5.34561061859131</v>
       </c>
       <c r="H408" t="n">
         <v>2000</v>
@@ -12230,7 +12230,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H409" t="n">
         <v>1500</v>
@@ -12259,7 +12259,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G410" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>7</v>
       </c>
       <c r="G412" t="n">
-        <v>5.42308378219604</v>
+        <v>5.4230842590332</v>
       </c>
       <c r="H412" t="n">
         <v>5000</v>
@@ -12375,7 +12375,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H414" t="n">
         <v>500</v>
@@ -12404,7 +12404,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H415" t="n">
         <v>500</v>
@@ -12433,7 +12433,7 @@
         <v>6.5</v>
       </c>
       <c r="G416" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H416" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H417" t="n">
         <v>1000</v>
@@ -12491,7 +12491,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G423" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H423" t="n">
         <v>500</v>
@@ -12665,7 +12665,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G427" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G428" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H428" t="n">
         <v>500</v>
@@ -12810,7 +12810,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G429" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G430" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G432" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H442" t="n">
         <v>1500</v>
@@ -13216,7 +13216,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13274,7 +13274,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G446" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G447" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>6.75</v>
       </c>
       <c r="G448" t="n">
-        <v>5.2294020652771</v>
+        <v>5.22940254211426</v>
       </c>
       <c r="H448" t="n">
         <v>6500</v>
@@ -13390,7 +13390,7 @@
         <v>6.75</v>
       </c>
       <c r="G449" t="n">
-        <v>5.2294020652771</v>
+        <v>5.22940254211426</v>
       </c>
       <c r="H449" t="n">
         <v>5500</v>
@@ -13419,7 +13419,7 @@
         <v>7</v>
       </c>
       <c r="G450" t="n">
-        <v>5.42308378219604</v>
+        <v>5.4230842590332</v>
       </c>
       <c r="H450" t="n">
         <v>3500</v>
@@ -13448,7 +13448,7 @@
         <v>7</v>
       </c>
       <c r="G451" t="n">
-        <v>5.42308378219604</v>
+        <v>5.4230842590332</v>
       </c>
       <c r="H451" t="n">
         <v>6500</v>
@@ -13477,7 +13477,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>5.34561157226562</v>
+        <v>5.34561061859131</v>
       </c>
       <c r="H452" t="n">
         <v>4000</v>
@@ -13506,7 +13506,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>5.30687475204468</v>
+        <v>5.30687522888184</v>
       </c>
       <c r="H453" t="n">
         <v>1500</v>
@@ -13535,7 +13535,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.30687475204468</v>
+        <v>5.30687522888184</v>
       </c>
       <c r="H454" t="n">
         <v>1500</v>
@@ -13564,7 +13564,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G455" t="n">
-        <v>5.30687475204468</v>
+        <v>5.30687522888184</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>5.46182012557983</v>
+        <v>5.46181964874268</v>
       </c>
       <c r="H458" t="n">
         <v>11000</v>
@@ -13680,7 +13680,7 @@
         <v>7</v>
       </c>
       <c r="G459" t="n">
-        <v>5.42308378219604</v>
+        <v>5.4230842590332</v>
       </c>
       <c r="H459" t="n">
         <v>4000</v>
@@ -13709,7 +13709,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>5.30687475204468</v>
+        <v>5.30687522888184</v>
       </c>
       <c r="H460" t="n">
         <v>1000</v>
@@ -13738,7 +13738,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>5.34561157226562</v>
+        <v>5.34561061859131</v>
       </c>
       <c r="H461" t="n">
         <v>9000</v>
@@ -13825,7 +13825,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>5.46182012557983</v>
+        <v>5.46181964874268</v>
       </c>
       <c r="H464" t="n">
         <v>500</v>
@@ -13854,7 +13854,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>5.46182012557983</v>
+        <v>5.46181964874268</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G466" t="n">
-        <v>5.46182012557983</v>
+        <v>5.46181964874268</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34561157226562</v>
+        <v>5.34561061859131</v>
       </c>
       <c r="H467" t="n">
         <v>500</v>
@@ -13941,7 +13941,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G468" t="n">
-        <v>5.34561157226562</v>
+        <v>5.34561061859131</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>6.75</v>
       </c>
       <c r="G469" t="n">
-        <v>5.2294020652771</v>
+        <v>5.22940254211426</v>
       </c>
       <c r="H469" t="n">
         <v>500</v>
@@ -13999,7 +13999,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G470" t="n">
-        <v>5.34561157226562</v>
+        <v>5.34561061859131</v>
       </c>
       <c r="H470" t="n">
         <v>32500</v>
@@ -14028,7 +14028,7 @@
         <v>6.75</v>
       </c>
       <c r="G471" t="n">
-        <v>5.2294020652771</v>
+        <v>5.22940254211426</v>
       </c>
       <c r="H471" t="n">
         <v>4500</v>
@@ -14115,7 +14115,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G474" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H474" t="n">
         <v>1000</v>
@@ -14144,7 +14144,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H475" t="n">
         <v>3500</v>
@@ -14173,7 +14173,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.80330324172974</v>
+        <v>4.80330228805542</v>
       </c>
       <c r="H476" t="n">
         <v>51000</v>
@@ -14202,7 +14202,7 @@
         <v>6.25</v>
       </c>
       <c r="G477" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H477" t="n">
         <v>3000</v>
@@ -14231,7 +14231,7 @@
         <v>6.25</v>
       </c>
       <c r="G478" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
         <v>6.25</v>
       </c>
       <c r="G479" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G480" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H480" t="n">
         <v>3000</v>
@@ -14318,7 +14318,7 @@
         <v>6.25</v>
       </c>
       <c r="G481" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H481" t="n">
         <v>500</v>
@@ -14376,7 +14376,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.80330324172974</v>
+        <v>4.80330228805542</v>
       </c>
       <c r="H483" t="n">
         <v>500</v>
@@ -14405,7 +14405,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H484" t="n">
         <v>20000</v>
@@ -14434,7 +14434,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>6.25</v>
       </c>
       <c r="G486" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H486" t="n">
         <v>500</v>
@@ -14492,7 +14492,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G487" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H487" t="n">
         <v>1500</v>
@@ -14521,7 +14521,7 @@
         <v>6.25</v>
       </c>
       <c r="G488" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H488" t="n">
         <v>500</v>
@@ -14550,7 +14550,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G489" t="n">
-        <v>4.80330324172974</v>
+        <v>4.80330228805542</v>
       </c>
       <c r="H489" t="n">
         <v>1500</v>
@@ -14579,7 +14579,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.80330324172974</v>
+        <v>4.80330228805542</v>
       </c>
       <c r="H490" t="n">
         <v>0</v>
@@ -14608,7 +14608,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.80330324172974</v>
+        <v>4.80330228805542</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>6.25</v>
       </c>
       <c r="G498" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H498" t="n">
         <v>500</v>
@@ -14840,7 +14840,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>4.88077545166016</v>
+        <v>4.88077592849731</v>
       </c>
       <c r="H499" t="n">
         <v>1500</v>
@@ -14869,7 +14869,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>4.88077545166016</v>
+        <v>4.88077592849731</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>4.88077545166016</v>
+        <v>4.88077592849731</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>6.25</v>
       </c>
       <c r="G502" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H502" t="n">
         <v>1500</v>
@@ -14956,7 +14956,7 @@
         <v>6.25</v>
       </c>
       <c r="G503" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>6.25</v>
       </c>
       <c r="G504" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>6.25</v>
       </c>
       <c r="G505" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>6.25</v>
       </c>
       <c r="G506" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>6.25</v>
       </c>
       <c r="G507" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>6.25</v>
       </c>
       <c r="G508" t="n">
-        <v>4.84203863143921</v>
+        <v>4.84203910827637</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G510" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H510" t="n">
         <v>500</v>
@@ -15188,7 +15188,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H512" t="n">
         <v>2000</v>
@@ -15246,7 +15246,7 @@
         <v>6.5</v>
       </c>
       <c r="G513" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H513" t="n">
         <v>1000</v>
@@ -15275,7 +15275,7 @@
         <v>6.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H515" t="n">
         <v>500</v>
@@ -15333,7 +15333,7 @@
         <v>6.5</v>
       </c>
       <c r="G516" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H516" t="n">
         <v>500</v>
@@ -15362,7 +15362,7 @@
         <v>6.5</v>
       </c>
       <c r="G517" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>6.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>6.5</v>
       </c>
       <c r="G519" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H520" t="n">
         <v>500</v>
@@ -15478,7 +15478,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G521" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H521" t="n">
         <v>3000</v>
@@ -15507,7 +15507,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G522" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H523" t="n">
         <v>0</v>
@@ -15565,7 +15565,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.60962057113647</v>
+        <v>4.60962152481079</v>
       </c>
       <c r="H524" t="n">
         <v>1000</v>
@@ -15594,7 +15594,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G525" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H525" t="n">
         <v>500</v>
@@ -15623,7 +15623,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G526" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G528" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G529" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G531" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H531" t="n">
         <v>0</v>
@@ -15797,7 +15797,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G532" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G538" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H538" t="n">
         <v>1000</v>
@@ -16000,7 +16000,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G539" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G540" t="n">
-        <v>4.68709373474121</v>
+        <v>4.68709421157837</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.725830078125</v>
+        <v>4.72583055496216</v>
       </c>
       <c r="H541" t="n">
         <v>500</v>
@@ -16087,7 +16087,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.725830078125</v>
+        <v>4.72583055496216</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>6.5</v>
       </c>
       <c r="G543" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H543" t="n">
         <v>1500</v>
@@ -16145,7 +16145,7 @@
         <v>6.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H544" t="n">
         <v>7000</v>
@@ -16174,7 +16174,7 @@
         <v>6.5</v>
       </c>
       <c r="G545" t="n">
-        <v>5.03572082519531</v>
+        <v>5.03572034835815</v>
       </c>
       <c r="H545" t="n">
         <v>500</v>
@@ -16203,7 +16203,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G546" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H546" t="n">
         <v>500</v>
@@ -16232,7 +16232,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>4.95824813842773</v>
+        <v>4.95824861526489</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H551" t="n">
         <v>1500</v>
@@ -16377,7 +16377,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G552" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>4.99698448181152</v>
+        <v>4.99698400497437</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.88077545166016</v>
+        <v>4.88077592849731</v>
       </c>
       <c r="H554" t="n">
         <v>500</v>
@@ -16464,7 +16464,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>4.88077545166016</v>
+        <v>4.88077592849731</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H556" t="n">
         <v>4500</v>
@@ -16522,7 +16522,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H557" t="n">
         <v>0</v>
@@ -16638,7 +16638,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H561" t="n">
         <v>500</v>
@@ -16667,7 +16667,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>6.75</v>
       </c>
       <c r="G563" t="n">
-        <v>5.2294020652771</v>
+        <v>5.22940254211426</v>
       </c>
       <c r="H563" t="n">
         <v>500</v>
@@ -16725,7 +16725,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>5.07445669174194</v>
+        <v>5.07445764541626</v>
       </c>
       <c r="H564" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H565" t="n">
         <v>500</v>
@@ -16783,7 +16783,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G567" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G572" t="n">
-        <v>5.15192937850952</v>
+        <v>5.15192985534668</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -17305,7 +17305,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>5.53929281234741</v>
+        <v>5.53929233551025</v>
       </c>
       <c r="H584" t="n">
         <v>2000</v>
@@ -17363,7 +17363,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G586" t="n">
-        <v>5.53929281234741</v>
+        <v>5.53929233551025</v>
       </c>
       <c r="H586" t="n">
         <v>5500</v>
@@ -17595,7 +17595,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G594" t="n">
-        <v>5.69423770904541</v>
+        <v>5.69423723220825</v>
       </c>
       <c r="H594" t="n">
         <v>500</v>
@@ -17682,7 +17682,7 @@
         <v>7.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.81044721603394</v>
+        <v>5.81044673919678</v>
       </c>
       <c r="H597" t="n">
         <v>4000</v>
@@ -17740,7 +17740,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.96539115905762</v>
+        <v>5.96539211273193</v>
       </c>
       <c r="H599" t="n">
         <v>26500</v>
@@ -17769,7 +17769,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G600" t="n">
-        <v>5.88791942596436</v>
+        <v>5.8879189491272</v>
       </c>
       <c r="H600" t="n">
         <v>24500</v>
@@ -17798,7 +17798,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>6.04286527633667</v>
+        <v>6.04286479949951</v>
       </c>
       <c r="H601" t="n">
         <v>7000</v>
@@ -17827,7 +17827,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>5.9266562461853</v>
+        <v>5.92665576934814</v>
       </c>
       <c r="H602" t="n">
         <v>4000</v>
@@ -17856,7 +17856,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G603" t="n">
-        <v>5.9266562461853</v>
+        <v>5.92665576934814</v>
       </c>
       <c r="H603" t="n">
         <v>4500</v>
@@ -17943,7 +17943,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>6.04286527633667</v>
+        <v>6.04286479949951</v>
       </c>
       <c r="H606" t="n">
         <v>2500</v>
@@ -17972,7 +17972,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>6.2050895690918</v>
+        <v>6.20508909225464</v>
       </c>
       <c r="H607" t="n">
         <v>6000</v>
@@ -18001,7 +18001,7 @@
         <v>7.5</v>
       </c>
       <c r="G608" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18030,7 +18030,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.12397766113281</v>
+        <v>6.12397718429565</v>
       </c>
       <c r="H609" t="n">
         <v>4000</v>
@@ -18059,7 +18059,7 @@
         <v>7.5</v>
       </c>
       <c r="G610" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H610" t="n">
         <v>4000</v>
@@ -18117,7 +18117,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G612" t="n">
-        <v>6.12397766113281</v>
+        <v>6.12397718429565</v>
       </c>
       <c r="H612" t="n">
         <v>3000</v>
@@ -18146,7 +18146,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G613" t="n">
-        <v>6.24564504623413</v>
+        <v>6.24564552307129</v>
       </c>
       <c r="H613" t="n">
         <v>1500</v>
@@ -18175,7 +18175,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H614" t="n">
         <v>1500</v>
@@ -18204,7 +18204,7 @@
         <v>7.5</v>
       </c>
       <c r="G615" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H615" t="n">
         <v>1500</v>
@@ -18233,7 +18233,7 @@
         <v>7.5</v>
       </c>
       <c r="G616" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H616" t="n">
         <v>2000</v>
@@ -18291,7 +18291,7 @@
         <v>7.5</v>
       </c>
       <c r="G618" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H618" t="n">
         <v>2500</v>
@@ -18320,7 +18320,7 @@
         <v>7.5</v>
       </c>
       <c r="G619" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G620" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H620" t="n">
         <v>2500</v>
@@ -18436,7 +18436,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H623" t="n">
         <v>2500</v>
@@ -18465,7 +18465,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G624" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H624" t="n">
         <v>500</v>
@@ -18552,7 +18552,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.12397766113281</v>
+        <v>6.12397718429565</v>
       </c>
       <c r="H627" t="n">
         <v>500</v>
@@ -18581,7 +18581,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.12397766113281</v>
+        <v>6.12397718429565</v>
       </c>
       <c r="H628" t="n">
         <v>0</v>
@@ -18697,7 +18697,7 @@
         <v>7.25</v>
       </c>
       <c r="G632" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H632" t="n">
         <v>3500</v>
@@ -18726,7 +18726,7 @@
         <v>7.25</v>
       </c>
       <c r="G633" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.75897216796875</v>
+        <v>5.75897121429443</v>
       </c>
       <c r="H634" t="n">
         <v>5500</v>
@@ -18784,7 +18784,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G635" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H635" t="n">
         <v>1000</v>
@@ -18813,7 +18813,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G636" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H636" t="n">
         <v>1500</v>
@@ -18842,7 +18842,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H642" t="n">
         <v>5000</v>
@@ -19016,7 +19016,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H643" t="n">
         <v>3500</v>
@@ -19045,7 +19045,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G644" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H644" t="n">
         <v>2000</v>
@@ -19074,7 +19074,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G645" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H645" t="n">
         <v>500</v>
@@ -19103,7 +19103,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H646" t="n">
         <v>2000</v>
@@ -19132,7 +19132,7 @@
         <v>7.5</v>
       </c>
       <c r="G647" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H647" t="n">
         <v>1500</v>
@@ -19190,7 +19190,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G649" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H649" t="n">
         <v>1500</v>
@@ -19219,7 +19219,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G650" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H650" t="n">
         <v>1500</v>
@@ -19248,7 +19248,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H651" t="n">
         <v>3500</v>
@@ -19277,7 +19277,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G652" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H652" t="n">
         <v>1500</v>
@@ -19306,7 +19306,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G653" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H653" t="n">
         <v>2000</v>
@@ -19335,7 +19335,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H654" t="n">
         <v>500</v>
@@ -19364,7 +19364,7 @@
         <v>7.5</v>
       </c>
       <c r="G655" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H655" t="n">
         <v>8500</v>
@@ -19393,7 +19393,7 @@
         <v>7.5</v>
       </c>
       <c r="G656" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H656" t="n">
         <v>2000</v>
@@ -19451,7 +19451,7 @@
         <v>7.5</v>
       </c>
       <c r="G658" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H658" t="n">
         <v>3000</v>
@@ -19538,7 +19538,7 @@
         <v>7.5</v>
       </c>
       <c r="G661" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H661" t="n">
         <v>500</v>
@@ -19567,7 +19567,7 @@
         <v>7.5</v>
       </c>
       <c r="G662" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
         <v>7.5</v>
       </c>
       <c r="G663" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G665" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H665" t="n">
         <v>11000</v>
@@ -19683,7 +19683,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G666" t="n">
-        <v>6.12397766113281</v>
+        <v>6.12397718429565</v>
       </c>
       <c r="H666" t="n">
         <v>7000</v>
@@ -19712,7 +19712,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>6.12397766113281</v>
+        <v>6.12397718429565</v>
       </c>
       <c r="H667" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>7.5</v>
       </c>
       <c r="G669" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H669" t="n">
         <v>1000</v>
@@ -19799,7 +19799,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>6.2050895690918</v>
+        <v>6.20508909225464</v>
       </c>
       <c r="H670" t="n">
         <v>500</v>
@@ -19828,7 +19828,7 @@
         <v>7.5</v>
       </c>
       <c r="G671" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H671" t="n">
         <v>10500</v>
@@ -20031,7 +20031,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H678" t="n">
         <v>6500</v>
@@ -20060,7 +20060,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>7.5</v>
       </c>
       <c r="G681" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H681" t="n">
         <v>2500</v>
@@ -20147,7 +20147,7 @@
         <v>7.5</v>
       </c>
       <c r="G682" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H682" t="n">
         <v>1000</v>
@@ -20176,7 +20176,7 @@
         <v>7.25</v>
       </c>
       <c r="G683" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H683" t="n">
         <v>4500</v>
@@ -20205,7 +20205,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G684" t="n">
-        <v>5.75897216796875</v>
+        <v>5.75897121429443</v>
       </c>
       <c r="H684" t="n">
         <v>3500</v>
@@ -20234,7 +20234,7 @@
         <v>7.25</v>
       </c>
       <c r="G685" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H685" t="n">
         <v>500</v>
@@ -20263,7 +20263,7 @@
         <v>7.25</v>
       </c>
       <c r="G686" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H686" t="n">
         <v>1000</v>
@@ -20292,7 +20292,7 @@
         <v>7.25</v>
       </c>
       <c r="G687" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -20321,7 +20321,7 @@
         <v>7.25</v>
       </c>
       <c r="G688" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>7.25</v>
       </c>
       <c r="G689" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -20379,7 +20379,7 @@
         <v>7.25</v>
       </c>
       <c r="G690" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H690" t="n">
         <v>0</v>
@@ -20408,7 +20408,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G691" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H691" t="n">
         <v>1000</v>
@@ -20611,7 +20611,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G698" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H698" t="n">
         <v>2500</v>
@@ -20640,7 +20640,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -20669,7 +20669,7 @@
         <v>7.25</v>
       </c>
       <c r="G700" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H700" t="n">
         <v>2500</v>
@@ -20698,7 +20698,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H701" t="n">
         <v>2000</v>
@@ -20785,7 +20785,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H704" t="n">
         <v>1500</v>
@@ -20872,7 +20872,7 @@
         <v>7.25</v>
       </c>
       <c r="G707" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H707" t="n">
         <v>500</v>
@@ -20901,7 +20901,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G708" t="n">
-        <v>6.24564504623413</v>
+        <v>6.24564552307129</v>
       </c>
       <c r="H708" t="n">
         <v>19000</v>
@@ -20930,7 +20930,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G709" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H709" t="n">
         <v>2000</v>
@@ -20959,7 +20959,7 @@
         <v>7.5</v>
       </c>
       <c r="G710" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H710" t="n">
         <v>3000</v>
@@ -20988,7 +20988,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G711" t="n">
-        <v>6.24564504623413</v>
+        <v>6.24564552307129</v>
       </c>
       <c r="H711" t="n">
         <v>8000</v>
@@ -21017,7 +21017,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G712" t="n">
-        <v>6.24564504623413</v>
+        <v>6.24564552307129</v>
       </c>
       <c r="H712" t="n">
         <v>2500</v>
@@ -21046,7 +21046,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G713" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H713" t="n">
         <v>3500</v>
@@ -21220,7 +21220,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H719" t="n">
         <v>2000</v>
@@ -21307,7 +21307,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G722" t="n">
-        <v>5.75897216796875</v>
+        <v>5.75897121429443</v>
       </c>
       <c r="H722" t="n">
         <v>7500</v>
@@ -21365,7 +21365,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H724" t="n">
         <v>1500</v>
@@ -21394,7 +21394,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G725" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H726" t="n">
         <v>500</v>
@@ -21655,7 +21655,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>6.12397766113281</v>
+        <v>6.12397718429565</v>
       </c>
       <c r="H734" t="n">
         <v>1500</v>
@@ -21713,7 +21713,7 @@
         <v>7.5</v>
       </c>
       <c r="G736" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H736" t="n">
         <v>500</v>
@@ -21742,7 +21742,7 @@
         <v>7.5</v>
       </c>
       <c r="G737" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H737" t="n">
         <v>500</v>
@@ -21771,7 +21771,7 @@
         <v>7.5</v>
       </c>
       <c r="G738" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H738" t="n">
         <v>1500</v>
@@ -21800,7 +21800,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G739" t="n">
-        <v>6.12397766113281</v>
+        <v>6.12397718429565</v>
       </c>
       <c r="H739" t="n">
         <v>3500</v>
@@ -21829,7 +21829,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H740" t="n">
         <v>10000</v>
@@ -21858,7 +21858,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>6.24564504623413</v>
+        <v>6.24564552307129</v>
       </c>
       <c r="H741" t="n">
         <v>3000</v>
@@ -21887,7 +21887,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H742" t="n">
         <v>6500</v>
@@ -21916,7 +21916,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G743" t="n">
-        <v>6.85398817062378</v>
+        <v>6.85398721694946</v>
       </c>
       <c r="H743" t="n">
         <v>38500</v>
@@ -21945,7 +21945,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G744" t="n">
-        <v>7.86789178848267</v>
+        <v>7.86788988113403</v>
       </c>
       <c r="H744" t="n">
         <v>134000</v>
@@ -22003,7 +22003,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G746" t="n">
-        <v>7.42177391052246</v>
+        <v>7.42177295684814</v>
       </c>
       <c r="H746" t="n">
         <v>41500</v>
@@ -22032,7 +22032,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>7.34066104888916</v>
+        <v>7.34066152572632</v>
       </c>
       <c r="H747" t="n">
         <v>13500</v>
@@ -22061,7 +22061,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>7.13788175582886</v>
+        <v>7.1378812789917</v>
       </c>
       <c r="H748" t="n">
         <v>4000</v>
@@ -22090,7 +22090,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G749" t="n">
-        <v>6.97565603256226</v>
+        <v>6.97565650939941</v>
       </c>
       <c r="H749" t="n">
         <v>4500</v>
@@ -22119,7 +22119,7 @@
         <v>9</v>
       </c>
       <c r="G750" t="n">
-        <v>7.30010461807251</v>
+        <v>7.30010557174683</v>
       </c>
       <c r="H750" t="n">
         <v>9500</v>
@@ -22177,7 +22177,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>7.13788175582886</v>
+        <v>7.1378812789917</v>
       </c>
       <c r="H752" t="n">
         <v>2000</v>
@@ -22235,7 +22235,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G754" t="n">
-        <v>7.21899271011353</v>
+        <v>7.21899175643921</v>
       </c>
       <c r="H754" t="n">
         <v>7500</v>
@@ -22293,7 +22293,7 @@
         <v>9</v>
       </c>
       <c r="G756" t="n">
-        <v>7.30010461807251</v>
+        <v>7.30010557174683</v>
       </c>
       <c r="H756" t="n">
         <v>6500</v>
@@ -22351,7 +22351,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>7.13788175582886</v>
+        <v>7.1378812789917</v>
       </c>
       <c r="H758" t="n">
         <v>4000</v>
@@ -22380,7 +22380,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G759" t="n">
-        <v>7.21899271011353</v>
+        <v>7.21899175643921</v>
       </c>
       <c r="H759" t="n">
         <v>2000</v>
@@ -22409,7 +22409,7 @@
         <v>9</v>
       </c>
       <c r="G760" t="n">
-        <v>7.30010461807251</v>
+        <v>7.30010557174683</v>
       </c>
       <c r="H760" t="n">
         <v>1000</v>
@@ -22496,7 +22496,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G763" t="n">
-        <v>7.21899271011353</v>
+        <v>7.21899175643921</v>
       </c>
       <c r="H763" t="n">
         <v>4000</v>
@@ -22525,7 +22525,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G764" t="n">
-        <v>7.05676746368408</v>
+        <v>7.0567684173584</v>
       </c>
       <c r="H764" t="n">
         <v>4500</v>
@@ -22583,7 +22583,7 @@
         <v>9</v>
       </c>
       <c r="G766" t="n">
-        <v>7.30010461807251</v>
+        <v>7.30010557174683</v>
       </c>
       <c r="H766" t="n">
         <v>500</v>
@@ -22612,7 +22612,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="n">
-        <v>7.30010461807251</v>
+        <v>7.30010557174683</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G768" t="n">
-        <v>7.17843627929688</v>
+        <v>7.17843675613403</v>
       </c>
       <c r="H768" t="n">
         <v>3000</v>
@@ -22670,7 +22670,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>7.05676746368408</v>
+        <v>7.0567684173584</v>
       </c>
       <c r="H769" t="n">
         <v>1000</v>
@@ -22699,7 +22699,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G770" t="n">
-        <v>6.77287530899048</v>
+        <v>6.77287578582764</v>
       </c>
       <c r="H770" t="n">
         <v>10500</v>
@@ -22786,7 +22786,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>7.05676746368408</v>
+        <v>7.0567684173584</v>
       </c>
       <c r="H773" t="n">
         <v>4500</v>
@@ -22815,7 +22815,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G774" t="n">
-        <v>7.13788175582886</v>
+        <v>7.1378812789917</v>
       </c>
       <c r="H774" t="n">
         <v>8000</v>
@@ -22844,7 +22844,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>7.13788175582886</v>
+        <v>7.1378812789917</v>
       </c>
       <c r="H775" t="n">
         <v>2000</v>
@@ -22873,7 +22873,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G776" t="n">
-        <v>7.01621150970459</v>
+        <v>7.01621103286743</v>
       </c>
       <c r="H776" t="n">
         <v>500</v>
@@ -22902,7 +22902,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G777" t="n">
-        <v>7.01621150970459</v>
+        <v>7.01621103286743</v>
       </c>
       <c r="H777" t="n">
         <v>0</v>
@@ -22931,7 +22931,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G778" t="n">
-        <v>7.01621150970459</v>
+        <v>7.01621103286743</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -22960,7 +22960,7 @@
         <v>9</v>
       </c>
       <c r="G779" t="n">
-        <v>7.30010461807251</v>
+        <v>7.30010557174683</v>
       </c>
       <c r="H779" t="n">
         <v>2500</v>
@@ -22989,7 +22989,7 @@
         <v>9</v>
       </c>
       <c r="G780" t="n">
-        <v>7.30010461807251</v>
+        <v>7.30010557174683</v>
       </c>
       <c r="H780" t="n">
         <v>1000</v>
@@ -23018,7 +23018,7 @@
         <v>9</v>
       </c>
       <c r="G781" t="n">
-        <v>7.30010461807251</v>
+        <v>7.30010557174683</v>
       </c>
       <c r="H781" t="n">
         <v>2000</v>
@@ -23134,7 +23134,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G785" t="n">
-        <v>7.21899271011353</v>
+        <v>7.21899175643921</v>
       </c>
       <c r="H785" t="n">
         <v>4500</v>
@@ -23221,7 +23221,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>7.05676746368408</v>
+        <v>7.0567684173584</v>
       </c>
       <c r="H788" t="n">
         <v>5500</v>
@@ -23250,7 +23250,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>7.13788175582886</v>
+        <v>7.1378812789917</v>
       </c>
       <c r="H789" t="n">
         <v>2500</v>
@@ -23308,7 +23308,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G791" t="n">
-        <v>7.17843627929688</v>
+        <v>7.17843675613403</v>
       </c>
       <c r="H791" t="n">
         <v>1500</v>
@@ -23337,7 +23337,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G792" t="n">
-        <v>7.21899271011353</v>
+        <v>7.21899175643921</v>
       </c>
       <c r="H792" t="n">
         <v>4500</v>
@@ -23366,7 +23366,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G793" t="n">
-        <v>7.54344272613525</v>
+        <v>7.54344177246094</v>
       </c>
       <c r="H793" t="n">
         <v>18500</v>
@@ -23424,7 +23424,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G795" t="n">
-        <v>7.54344272613525</v>
+        <v>7.54344177246094</v>
       </c>
       <c r="H795" t="n">
         <v>6000</v>
@@ -23540,7 +23540,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G799" t="n">
-        <v>7.13788175582886</v>
+        <v>7.1378812789917</v>
       </c>
       <c r="H799" t="n">
         <v>1500</v>
@@ -23598,7 +23598,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G801" t="n">
-        <v>7.13788175582886</v>
+        <v>7.1378812789917</v>
       </c>
       <c r="H801" t="n">
         <v>1500</v>
@@ -23656,7 +23656,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G803" t="n">
-        <v>7.05676746368408</v>
+        <v>7.0567684173584</v>
       </c>
       <c r="H803" t="n">
         <v>500</v>
@@ -23685,7 +23685,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G804" t="n">
-        <v>7.05676746368408</v>
+        <v>7.0567684173584</v>
       </c>
       <c r="H804" t="n">
         <v>4500</v>
@@ -23830,7 +23830,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G809" t="n">
-        <v>7.21899271011353</v>
+        <v>7.21899175643921</v>
       </c>
       <c r="H809" t="n">
         <v>3000</v>
@@ -24149,7 +24149,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G820" t="n">
-        <v>7.42177391052246</v>
+        <v>7.42177295684814</v>
       </c>
       <c r="H820" t="n">
         <v>9500</v>
@@ -24323,7 +24323,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G826" t="n">
-        <v>7.42177391052246</v>
+        <v>7.42177295684814</v>
       </c>
       <c r="H826" t="n">
         <v>3500</v>
@@ -24410,7 +24410,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G829" t="n">
-        <v>7.34066104888916</v>
+        <v>7.34066152572632</v>
       </c>
       <c r="H829" t="n">
         <v>31000</v>
@@ -24439,7 +24439,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G830" t="n">
-        <v>7.21899271011353</v>
+        <v>7.21899175643921</v>
       </c>
       <c r="H830" t="n">
         <v>1000</v>
@@ -24468,7 +24468,7 @@
         <v>9</v>
       </c>
       <c r="G831" t="n">
-        <v>7.30010461807251</v>
+        <v>7.30010557174683</v>
       </c>
       <c r="H831" t="n">
         <v>2000</v>
@@ -24526,7 +24526,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G833" t="n">
-        <v>7.21899271011353</v>
+        <v>7.21899175643921</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G834" t="n">
-        <v>6.97565603256226</v>
+        <v>6.97565650939941</v>
       </c>
       <c r="H834" t="n">
         <v>6500</v>
@@ -24584,7 +24584,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G835" t="n">
-        <v>6.97565603256226</v>
+        <v>6.97565650939941</v>
       </c>
       <c r="H835" t="n">
         <v>2500</v>
@@ -24700,7 +24700,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G839" t="n">
-        <v>6.52953815460205</v>
+        <v>6.52953910827637</v>
       </c>
       <c r="H839" t="n">
         <v>15000</v>
@@ -24932,7 +24932,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>7.13788175582886</v>
+        <v>7.1378812789917</v>
       </c>
       <c r="H847" t="n">
         <v>10500</v>
@@ -24961,7 +24961,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G848" t="n">
-        <v>6.97565603256226</v>
+        <v>6.97565650939941</v>
       </c>
       <c r="H848" t="n">
         <v>4500</v>
@@ -24990,7 +24990,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G849" t="n">
-        <v>6.97565603256226</v>
+        <v>6.97565650939941</v>
       </c>
       <c r="H849" t="n">
         <v>2000</v>
@@ -25019,7 +25019,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G850" t="n">
-        <v>6.97565603256226</v>
+        <v>6.97565650939941</v>
       </c>
       <c r="H850" t="n">
         <v>10500</v>
@@ -25048,7 +25048,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G851" t="n">
-        <v>7.01621150970459</v>
+        <v>7.01621103286743</v>
       </c>
       <c r="H851" t="n">
         <v>500</v>
@@ -25135,7 +25135,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G854" t="n">
-        <v>6.40786981582642</v>
+        <v>6.40786933898926</v>
       </c>
       <c r="H854" t="n">
         <v>3000</v>
@@ -25222,7 +25222,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>6.40786981582642</v>
+        <v>6.40786933898926</v>
       </c>
       <c r="H857" t="n">
         <v>1500</v>
@@ -25251,7 +25251,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G858" t="n">
-        <v>6.36731386184692</v>
+        <v>6.36731433868408</v>
       </c>
       <c r="H858" t="n">
         <v>4500</v>
@@ -25280,7 +25280,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G859" t="n">
-        <v>6.2050895690918</v>
+        <v>6.20508909225464</v>
       </c>
       <c r="H859" t="n">
         <v>5500</v>
@@ -25367,7 +25367,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H862" t="n">
         <v>10500</v>
@@ -25396,7 +25396,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G863" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H863" t="n">
         <v>1000</v>
@@ -25454,7 +25454,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G865" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H865" t="n">
         <v>5000</v>
@@ -25483,7 +25483,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G866" t="n">
-        <v>6.2050895690918</v>
+        <v>6.20508909225464</v>
       </c>
       <c r="H866" t="n">
         <v>3000</v>
@@ -25512,7 +25512,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>6.12397766113281</v>
+        <v>6.12397718429565</v>
       </c>
       <c r="H867" t="n">
         <v>3000</v>
@@ -25541,7 +25541,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G868" t="n">
-        <v>6.2050895690918</v>
+        <v>6.20508909225464</v>
       </c>
       <c r="H868" t="n">
         <v>4000</v>
@@ -25570,7 +25570,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G869" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H869" t="n">
         <v>500</v>
@@ -25599,7 +25599,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G870" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H870" t="n">
         <v>3000</v>
@@ -25628,7 +25628,7 @@
         <v>7.5</v>
       </c>
       <c r="G871" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H871" t="n">
         <v>4000</v>
@@ -25657,7 +25657,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G872" t="n">
-        <v>5.75897216796875</v>
+        <v>5.75897121429443</v>
       </c>
       <c r="H872" t="n">
         <v>14500</v>
@@ -25715,7 +25715,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G874" t="n">
-        <v>5.75897216796875</v>
+        <v>5.75897121429443</v>
       </c>
       <c r="H874" t="n">
         <v>9500</v>
@@ -25744,7 +25744,7 @@
         <v>7.25</v>
       </c>
       <c r="G875" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H875" t="n">
         <v>500</v>
@@ -25860,7 +25860,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G879" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H879" t="n">
         <v>500</v>
@@ -25889,7 +25889,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G880" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H880" t="n">
         <v>500</v>
@@ -25918,7 +25918,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G881" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H881" t="n">
         <v>1000</v>
@@ -25947,7 +25947,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G882" t="n">
-        <v>5.75897216796875</v>
+        <v>5.75897121429443</v>
       </c>
       <c r="H882" t="n">
         <v>1500</v>
@@ -25976,7 +25976,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G883" t="n">
-        <v>5.75897216796875</v>
+        <v>5.75897121429443</v>
       </c>
       <c r="H883" t="n">
         <v>500</v>
@@ -26005,7 +26005,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>5.59674787521362</v>
+        <v>5.59674739837646</v>
       </c>
       <c r="H884" t="n">
         <v>4500</v>
@@ -26121,7 +26121,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G888" t="n">
-        <v>5.75897216796875</v>
+        <v>5.75897121429443</v>
       </c>
       <c r="H888" t="n">
         <v>1000</v>
@@ -26150,7 +26150,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G889" t="n">
-        <v>5.75897216796875</v>
+        <v>5.75897121429443</v>
       </c>
       <c r="H889" t="n">
         <v>1000</v>
@@ -26208,7 +26208,7 @@
         <v>7.25</v>
       </c>
       <c r="G891" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H891" t="n">
         <v>1500</v>
@@ -26295,7 +26295,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G894" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H894" t="n">
         <v>2000</v>
@@ -26324,7 +26324,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G895" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -26353,7 +26353,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G896" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -26382,7 +26382,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G897" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -26411,7 +26411,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G898" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -26440,7 +26440,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G899" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H899" t="n">
         <v>1000</v>
@@ -26469,7 +26469,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G900" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -26585,7 +26585,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G904" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H904" t="n">
         <v>1000</v>
@@ -26614,7 +26614,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G905" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -26643,7 +26643,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -26672,7 +26672,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G907" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -26701,7 +26701,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G908" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26788,7 +26788,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G911" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H911" t="n">
         <v>500</v>
@@ -26817,7 +26817,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>7.25</v>
       </c>
       <c r="G913" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H913" t="n">
         <v>500</v>
@@ -26875,7 +26875,7 @@
         <v>7.25</v>
       </c>
       <c r="G914" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -26904,7 +26904,7 @@
         <v>7.25</v>
       </c>
       <c r="G915" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         <v>7.25</v>
       </c>
       <c r="G916" t="n">
-        <v>5.88064050674438</v>
+        <v>5.88064002990723</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H917" t="n">
         <v>500</v>
@@ -26991,7 +26991,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H918" t="n">
         <v>1000</v>
@@ -27020,7 +27020,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G919" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G921" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H921" t="n">
         <v>1000</v>
@@ -27107,7 +27107,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27136,7 +27136,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G923" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H923" t="n">
         <v>1500</v>
@@ -27165,7 +27165,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -27223,7 +27223,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G926" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H926" t="n">
         <v>500</v>
@@ -27252,7 +27252,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G929" t="n">
-        <v>5.59674787521362</v>
+        <v>5.59674739837646</v>
       </c>
       <c r="H929" t="n">
         <v>2000</v>
@@ -27339,7 +27339,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G930" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H930" t="n">
         <v>500</v>
@@ -27368,7 +27368,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G931" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27397,7 +27397,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G932" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -27426,7 +27426,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G933" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -27455,7 +27455,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G935" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H935" t="n">
         <v>1000</v>
@@ -27513,7 +27513,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G936" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H936" t="n">
         <v>500</v>
@@ -27542,7 +27542,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>5.79952812194824</v>
+        <v>5.79952907562256</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -27571,7 +27571,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G938" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H938" t="n">
         <v>500</v>
@@ -27600,7 +27600,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G939" t="n">
-        <v>5.71841526031494</v>
+        <v>5.7184157371521</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -27774,7 +27774,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G945" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H945" t="n">
         <v>1000</v>
@@ -27803,7 +27803,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G946" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G947" t="n">
-        <v>5.92119646072388</v>
+        <v>5.92119598388672</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27890,7 +27890,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G949" t="n">
-        <v>5.55619144439697</v>
+        <v>5.55619096755981</v>
       </c>
       <c r="H949" t="n">
         <v>15500</v>
@@ -27919,7 +27919,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G950" t="n">
-        <v>5.6373028755188</v>
+        <v>5.63730335235596</v>
       </c>
       <c r="H950" t="n">
         <v>500</v>
@@ -28383,7 +28383,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G966" t="n">
-        <v>5.51563453674316</v>
+        <v>5.51563501358032</v>
       </c>
       <c r="H966" t="n">
         <v>9500</v>
@@ -28412,7 +28412,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G967" t="n">
-        <v>5.43452215194702</v>
+        <v>5.43452167510986</v>
       </c>
       <c r="H967" t="n">
         <v>11000</v>
@@ -28441,7 +28441,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G968" t="n">
-        <v>5.43452215194702</v>
+        <v>5.43452167510986</v>
       </c>
       <c r="H968" t="n">
         <v>2000</v>
@@ -28470,7 +28470,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G969" t="n">
-        <v>5.43452215194702</v>
+        <v>5.43452167510986</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -28499,7 +28499,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G970" t="n">
-        <v>5.55619144439697</v>
+        <v>5.55619096755981</v>
       </c>
       <c r="H970" t="n">
         <v>1500</v>
@@ -28586,7 +28586,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>5.55619144439697</v>
+        <v>5.55619096755981</v>
       </c>
       <c r="H973" t="n">
         <v>1000</v>
@@ -28615,7 +28615,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G974" t="n">
-        <v>5.55619144439697</v>
+        <v>5.55619096755981</v>
       </c>
       <c r="H974" t="n">
         <v>2000</v>
@@ -28818,7 +28818,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G981" t="n">
-        <v>5.6373028755188</v>
+        <v>5.63730335235596</v>
       </c>
       <c r="H981" t="n">
         <v>1000</v>
@@ -28847,7 +28847,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>5.55619144439697</v>
+        <v>5.55619096755981</v>
       </c>
       <c r="H982" t="n">
         <v>1500</v>
@@ -28876,7 +28876,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G983" t="n">
-        <v>5.55619144439697</v>
+        <v>5.55619096755981</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28905,7 +28905,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G984" t="n">
-        <v>5.51563453674316</v>
+        <v>5.51563501358032</v>
       </c>
       <c r="H984" t="n">
         <v>500</v>
@@ -28934,7 +28934,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G985" t="n">
-        <v>5.51563453674316</v>
+        <v>5.51563501358032</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -28963,7 +28963,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>5.31285429000854</v>
+        <v>5.3128547668457</v>
       </c>
       <c r="H986" t="n">
         <v>1000</v>
@@ -28992,7 +28992,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G987" t="n">
-        <v>5.39396667480469</v>
+        <v>5.39396715164185</v>
       </c>
       <c r="H987" t="n">
         <v>500</v>
@@ -29021,7 +29021,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G988" t="n">
-        <v>5.31285429000854</v>
+        <v>5.3128547668457</v>
       </c>
       <c r="H988" t="n">
         <v>500</v>
@@ -29050,7 +29050,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G989" t="n">
-        <v>5.31285429000854</v>
+        <v>5.3128547668457</v>
       </c>
       <c r="H989" t="n">
         <v>3000</v>
@@ -29079,7 +29079,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G990" t="n">
-        <v>5.39396667480469</v>
+        <v>5.39396715164185</v>
       </c>
       <c r="H990" t="n">
         <v>1000</v>
@@ -29108,7 +29108,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G991" t="n">
-        <v>5.31285429000854</v>
+        <v>5.3128547668457</v>
       </c>
       <c r="H991" t="n">
         <v>1000</v>
@@ -29137,7 +29137,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G992" t="n">
-        <v>5.31285429000854</v>
+        <v>5.3128547668457</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -29166,7 +29166,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="n">
-        <v>5.02896165847778</v>
+        <v>5.02896118164062</v>
       </c>
       <c r="H993" t="n">
         <v>6000</v>
@@ -29195,7 +29195,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G994" t="n">
-        <v>5.02896165847778</v>
+        <v>5.02896118164062</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -29224,7 +29224,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G995" t="n">
-        <v>5.02896165847778</v>
+        <v>5.02896118164062</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -29253,7 +29253,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G996" t="n">
-        <v>5.02896165847778</v>
+        <v>5.02896118164062</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G997" t="n">
-        <v>5.11007356643677</v>
+        <v>5.11007404327393</v>
       </c>
       <c r="H997" t="n">
         <v>500</v>
@@ -29311,7 +29311,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G998" t="n">
-        <v>5.11007356643677</v>
+        <v>5.11007404327393</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -29340,7 +29340,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G999" t="n">
-        <v>5.11007356643677</v>
+        <v>5.11007404327393</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.31285429000854</v>
+        <v>5.3128547668457</v>
       </c>
       <c r="H1001" t="n">
         <v>1000</v>
@@ -29427,7 +29427,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1002" t="n">
-        <v>5.51563453674316</v>
+        <v>5.51563501358032</v>
       </c>
       <c r="H1002" t="n">
         <v>1000</v>
@@ -29456,7 +29456,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1003" t="n">
-        <v>5.43452215194702</v>
+        <v>5.43452167510986</v>
       </c>
       <c r="H1003" t="n">
         <v>500</v>
@@ -29485,7 +29485,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1004" t="n">
-        <v>5.59674787521362</v>
+        <v>5.59674739837646</v>
       </c>
       <c r="H1004" t="n">
         <v>2000</v>
@@ -29514,7 +29514,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1005" t="n">
-        <v>5.51563453674316</v>
+        <v>5.51563501358032</v>
       </c>
       <c r="H1005" t="n">
         <v>2000</v>
@@ -29543,7 +29543,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1006" t="n">
-        <v>5.55619144439697</v>
+        <v>5.55619096755981</v>
       </c>
       <c r="H1006" t="n">
         <v>500</v>
@@ -29572,7 +29572,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1007" t="n">
-        <v>5.55619144439697</v>
+        <v>5.55619096755981</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -29601,7 +29601,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.55619144439697</v>
+        <v>5.55619096755981</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -29630,7 +29630,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.51563453674316</v>
+        <v>5.51563501358032</v>
       </c>
       <c r="H1009" t="n">
         <v>2000</v>
@@ -29688,7 +29688,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H1011" t="n">
         <v>2000</v>
@@ -29804,7 +29804,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H1015" t="n">
         <v>1500</v>
@@ -29833,7 +29833,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1016" t="n">
-        <v>6.16453313827515</v>
+        <v>6.1645336151123</v>
       </c>
       <c r="H1016" t="n">
         <v>1500</v>
@@ -29862,7 +29862,7 @@
         <v>7.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>6.08342170715332</v>
+        <v>6.083420753479</v>
       </c>
       <c r="H1017" t="n">
         <v>500</v>
@@ -29891,7 +29891,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1018" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H1018" t="n">
         <v>500</v>
@@ -29920,7 +29920,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.96175289154053</v>
+        <v>5.96175241470337</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -30036,7 +30036,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1023" t="n">
-        <v>7.01621150970459</v>
+        <v>7.01621103286743</v>
       </c>
       <c r="H1023" t="n">
         <v>7000</v>
@@ -30065,7 +30065,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.97565603256226</v>
+        <v>6.97565650939941</v>
       </c>
       <c r="H1024" t="n">
         <v>8500</v>
@@ -30094,7 +30094,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1025" t="n">
-        <v>6.85398817062378</v>
+        <v>6.85398721694946</v>
       </c>
       <c r="H1025" t="n">
         <v>9000</v>
@@ -30123,7 +30123,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1026" t="n">
-        <v>6.93510007858276</v>
+        <v>6.93510055541992</v>
       </c>
       <c r="H1026" t="n">
         <v>7500</v>
@@ -30152,7 +30152,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.93510007858276</v>
+        <v>6.93510055541992</v>
       </c>
       <c r="H1027" t="n">
         <v>7500</v>
@@ -30181,7 +30181,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1028" t="n">
-        <v>7.01621150970459</v>
+        <v>7.01621103286743</v>
       </c>
       <c r="H1028" t="n">
         <v>4500</v>
@@ -30210,7 +30210,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1029" t="n">
-        <v>7.01621150970459</v>
+        <v>7.01621103286743</v>
       </c>
       <c r="H1029" t="n">
         <v>4000</v>
@@ -30297,7 +30297,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1032" t="n">
-        <v>7.05676746368408</v>
+        <v>7.0567684173584</v>
       </c>
       <c r="H1032" t="n">
         <v>6000</v>
@@ -30326,7 +30326,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1033" t="n">
-        <v>7.21899271011353</v>
+        <v>7.21899175643921</v>
       </c>
       <c r="H1033" t="n">
         <v>15500</v>
@@ -30384,7 +30384,7 @@
         <v>8.25</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.04812955856323</v>
+        <v>7.04812908172607</v>
       </c>
       <c r="H1035" t="n">
         <v>7000</v>
@@ -30471,7 +30471,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="n">
-        <v>7.00541257858276</v>
+        <v>7.00541305541992</v>
       </c>
       <c r="H1038" t="n">
         <v>5000</v>
@@ -30529,7 +30529,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1040" t="n">
-        <v>6.87726497650146</v>
+        <v>6.87726640701294</v>
       </c>
       <c r="H1040" t="n">
         <v>1500</v>
@@ -30558,7 +30558,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.79183340072632</v>
+        <v>6.79183292388916</v>
       </c>
       <c r="H1041" t="n">
         <v>4000</v>
@@ -30761,7 +30761,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.53553819656372</v>
+        <v>6.53553771972656</v>
       </c>
       <c r="H1048" t="n">
         <v>13500</v>
@@ -30848,7 +30848,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.57825326919556</v>
+        <v>6.57825374603271</v>
       </c>
       <c r="H1051" t="n">
         <v>500</v>
@@ -30877,7 +30877,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.53553819656372</v>
+        <v>6.53553771972656</v>
       </c>
       <c r="H1052" t="n">
         <v>2000</v>
@@ -30964,7 +30964,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.70640134811401</v>
+        <v>6.70640182495117</v>
       </c>
       <c r="H1055" t="n">
         <v>1500</v>
@@ -30993,7 +30993,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.70640134811401</v>
+        <v>6.70640182495117</v>
       </c>
       <c r="H1056" t="n">
         <v>500</v>
@@ -31022,7 +31022,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1057" t="n">
-        <v>6.79183340072632</v>
+        <v>6.79183292388916</v>
       </c>
       <c r="H1057" t="n">
         <v>3500</v>
@@ -31051,7 +31051,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.79183340072632</v>
+        <v>6.79183292388916</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -31428,7 +31428,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1071" t="n">
-        <v>6.45010662078857</v>
+        <v>6.45010614395142</v>
       </c>
       <c r="H1071" t="n">
         <v>18000</v>
@@ -31457,7 +31457,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1072" t="n">
-        <v>6.57825326919556</v>
+        <v>6.57825374603271</v>
       </c>
       <c r="H1072" t="n">
         <v>2000</v>
@@ -31486,7 +31486,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.57825326919556</v>
+        <v>6.57825374603271</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -31544,7 +31544,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.79183340072632</v>
+        <v>6.79183292388916</v>
       </c>
       <c r="H1075" t="n">
         <v>1500</v>
@@ -31602,7 +31602,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>6.87726497650146</v>
+        <v>6.87726640701294</v>
       </c>
       <c r="H1077" t="n">
         <v>1500</v>
@@ -31631,7 +31631,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.91998100280762</v>
+        <v>6.91998195648193</v>
       </c>
       <c r="H1078" t="n">
         <v>3000</v>
@@ -31660,7 +31660,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1079" t="n">
-        <v>7.13356065750122</v>
+        <v>7.13356161117554</v>
       </c>
       <c r="H1079" t="n">
         <v>16500</v>
@@ -31689,7 +31689,7 @@
         <v>8.25</v>
       </c>
       <c r="G1080" t="n">
-        <v>7.04812955856323</v>
+        <v>7.04812908172607</v>
       </c>
       <c r="H1080" t="n">
         <v>3500</v>
@@ -31718,7 +31718,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1081" t="n">
-        <v>7.13356065750122</v>
+        <v>7.13356161117554</v>
       </c>
       <c r="H1081" t="n">
         <v>500</v>
@@ -31776,7 +31776,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.30442476272583</v>
+        <v>7.30442523956299</v>
       </c>
       <c r="H1083" t="n">
         <v>5500</v>
@@ -31834,7 +31834,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1085" t="n">
-        <v>7.34714078903198</v>
+        <v>7.3471417427063</v>
       </c>
       <c r="H1085" t="n">
         <v>3000</v>
@@ -31863,7 +31863,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.34714078903198</v>
+        <v>7.3471417427063</v>
       </c>
       <c r="H1086" t="n">
         <v>1500</v>
@@ -31892,7 +31892,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1087" t="n">
-        <v>7.30442476272583</v>
+        <v>7.30442523956299</v>
       </c>
       <c r="H1087" t="n">
         <v>3000</v>
@@ -31921,7 +31921,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1088" t="n">
-        <v>7.30442476272583</v>
+        <v>7.30442523956299</v>
       </c>
       <c r="H1088" t="n">
         <v>5000</v>
@@ -31979,7 +31979,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="n">
-        <v>7.21899318695068</v>
+        <v>7.21899271011353</v>
       </c>
       <c r="H1090" t="n">
         <v>1500</v>
@@ -32008,7 +32008,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="n">
-        <v>7.21899318695068</v>
+        <v>7.21899271011353</v>
       </c>
       <c r="H1091" t="n">
         <v>0</v>
@@ -32037,7 +32037,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="n">
-        <v>7.21899318695068</v>
+        <v>7.21899271011353</v>
       </c>
       <c r="H1092" t="n">
         <v>0</v>
@@ -32066,7 +32066,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1093" t="n">
-        <v>7.30442476272583</v>
+        <v>7.30442523956299</v>
       </c>
       <c r="H1093" t="n">
         <v>2000</v>
@@ -32095,7 +32095,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.30442476272583</v>
+        <v>7.30442523956299</v>
       </c>
       <c r="H1094" t="n">
         <v>2500</v>
@@ -32124,7 +32124,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.30442476272583</v>
+        <v>7.30442523956299</v>
       </c>
       <c r="H1095" t="n">
         <v>0</v>
@@ -32153,7 +32153,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.51800537109375</v>
+        <v>7.51800489425659</v>
       </c>
       <c r="H1096" t="n">
         <v>6500</v>
@@ -32182,7 +32182,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1097" t="n">
-        <v>7.51800537109375</v>
+        <v>7.51800489425659</v>
       </c>
       <c r="H1097" t="n">
         <v>0</v>
@@ -32211,7 +32211,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1098" t="n">
-        <v>7.51800537109375</v>
+        <v>7.51800489425659</v>
       </c>
       <c r="H1098" t="n">
         <v>2500</v>
@@ -32240,7 +32240,7 @@
         <v>8.75</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.47528839111328</v>
+        <v>7.47528791427612</v>
       </c>
       <c r="H1099" t="n">
         <v>1500</v>
@@ -32269,7 +32269,7 @@
         <v>8.75</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.47528839111328</v>
+        <v>7.47528791427612</v>
       </c>
       <c r="H1100" t="n">
         <v>0</v>
@@ -32298,7 +32298,7 @@
         <v>8.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.47528839111328</v>
+        <v>7.47528791427612</v>
       </c>
       <c r="H1101" t="n">
         <v>0</v>
@@ -32327,7 +32327,7 @@
         <v>8.75</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.47528839111328</v>
+        <v>7.47528791427612</v>
       </c>
       <c r="H1102" t="n">
         <v>500</v>
@@ -32356,7 +32356,7 @@
         <v>8.75</v>
       </c>
       <c r="G1103" t="n">
-        <v>7.47528839111328</v>
+        <v>7.47528791427612</v>
       </c>
       <c r="H1103" t="n">
         <v>500</v>
@@ -32385,7 +32385,7 @@
         <v>8.75</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.47528839111328</v>
+        <v>7.47528791427612</v>
       </c>
       <c r="H1104" t="n">
         <v>0</v>
@@ -32414,7 +32414,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1105" t="n">
         <v>4000</v>
@@ -32443,7 +32443,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.34714078903198</v>
+        <v>7.3471417427063</v>
       </c>
       <c r="H1106" t="n">
         <v>1500</v>
@@ -32472,7 +32472,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1107" t="n">
         <v>1000</v>
@@ -32501,7 +32501,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1108" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1108" t="n">
         <v>0</v>
@@ -32530,7 +32530,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1109" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1109" t="n">
         <v>0</v>
@@ -32559,7 +32559,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1110" t="n">
         <v>0</v>
@@ -32588,7 +32588,7 @@
         <v>8.75</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.47528839111328</v>
+        <v>7.47528791427612</v>
       </c>
       <c r="H1111" t="n">
         <v>4000</v>
@@ -32617,7 +32617,7 @@
         <v>8.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.47528839111328</v>
+        <v>7.47528791427612</v>
       </c>
       <c r="H1112" t="n">
         <v>500</v>
@@ -32646,7 +32646,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1113" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1113" t="n">
         <v>1000</v>
@@ -32675,7 +32675,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1114" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1114" t="n">
         <v>0</v>
@@ -32704,7 +32704,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1115" t="n">
         <v>0</v>
@@ -32733,7 +32733,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1116" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1116" t="n">
         <v>0</v>
@@ -32762,7 +32762,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1117" t="n">
         <v>0</v>
@@ -32791,7 +32791,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1118" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1118" t="n">
         <v>500</v>
@@ -32820,7 +32820,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1119" t="n">
-        <v>7.43257141113281</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1119" t="n">
         <v>0</v>
@@ -32849,7 +32849,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1120" t="n">
-        <v>7.56296730041504</v>
+        <v>7.56296873092651</v>
       </c>
       <c r="H1120" t="n">
         <v>0</v>
@@ -32878,7 +32878,7 @@
         <v>8.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.6064338684082</v>
+        <v>7.60643291473389</v>
       </c>
       <c r="H1121" t="n">
         <v>1500</v>
@@ -32936,7 +32936,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.47603797912598</v>
+        <v>7.47603845596313</v>
       </c>
       <c r="H1123" t="n">
         <v>1000</v>
@@ -32965,7 +32965,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.47603797912598</v>
+        <v>7.47603845596313</v>
       </c>
       <c r="H1124" t="n">
         <v>0</v>
@@ -32994,7 +32994,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1125" t="n">
-        <v>7.47603797912598</v>
+        <v>7.47603845596313</v>
       </c>
       <c r="H1125" t="n">
         <v>0</v>
@@ -33023,7 +33023,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1126" t="n">
-        <v>7.47603797912598</v>
+        <v>7.47603845596313</v>
       </c>
       <c r="H1126" t="n">
         <v>0</v>
@@ -33052,7 +33052,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1127" t="n">
-        <v>7.56296730041504</v>
+        <v>7.56296873092651</v>
       </c>
       <c r="H1127" t="n">
         <v>3500</v>
@@ -33226,7 +33226,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1133" t="n">
-        <v>7.43257236480713</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1133" t="n">
         <v>2000</v>
@@ -33255,7 +33255,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1134" t="n">
-        <v>7.43257236480713</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1134" t="n">
         <v>0</v>
@@ -33313,7 +33313,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1136" t="n">
-        <v>7.43257236480713</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1136" t="n">
         <v>500</v>
@@ -33342,7 +33342,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>7.43257236480713</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1137" t="n">
         <v>500</v>
@@ -33371,7 +33371,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1138" t="n">
-        <v>7.43257236480713</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1138" t="n">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1139" t="n">
-        <v>7.43257236480713</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1139" t="n">
         <v>1500</v>
@@ -33429,7 +33429,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1140" t="n">
-        <v>7.43257236480713</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1140" t="n">
         <v>1500</v>
@@ -33458,7 +33458,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1141" t="n">
-        <v>7.43257236480713</v>
+        <v>7.43257331848145</v>
       </c>
       <c r="H1141" t="n">
         <v>500</v>
@@ -33487,7 +33487,7 @@
         <v>8.75</v>
       </c>
       <c r="G1142" t="n">
-        <v>7.6064338684082</v>
+        <v>7.60643291473389</v>
       </c>
       <c r="H1142" t="n">
         <v>2500</v>
@@ -33516,7 +33516,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1143" t="n">
-        <v>7.69336414337158</v>
+        <v>7.6933650970459</v>
       </c>
       <c r="H1143" t="n">
         <v>2000</v>
@@ -33545,7 +33545,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1144" t="n">
-        <v>7.64989995956421</v>
+        <v>7.64989948272705</v>
       </c>
       <c r="H1144" t="n">
         <v>1000</v>
@@ -33574,7 +33574,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1145" t="n">
-        <v>7.69336414337158</v>
+        <v>7.6933650970459</v>
       </c>
       <c r="H1145" t="n">
         <v>1500</v>
@@ -33603,7 +33603,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1146" t="n">
-        <v>7.69336414337158</v>
+        <v>7.6933650970459</v>
       </c>
       <c r="H1146" t="n">
         <v>1000</v>
@@ -33661,7 +33661,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1148" t="n">
-        <v>7.69336414337158</v>
+        <v>7.6933650970459</v>
       </c>
       <c r="H1148" t="n">
         <v>2000</v>
@@ -33719,7 +33719,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.73682928085327</v>
+        <v>7.73682832717896</v>
       </c>
       <c r="H1150" t="n">
         <v>1000</v>
@@ -33748,7 +33748,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.64989995956421</v>
+        <v>7.64989948272705</v>
       </c>
       <c r="H1151" t="n">
         <v>4000</v>
@@ -33777,7 +33777,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.64989995956421</v>
+        <v>7.64989948272705</v>
       </c>
       <c r="H1152" t="n">
         <v>139000</v>
@@ -33806,7 +33806,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1153" t="n">
-        <v>7.64989995956421</v>
+        <v>7.64989948272705</v>
       </c>
       <c r="H1153" t="n">
         <v>0</v>
@@ -33835,7 +33835,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1154" t="n">
-        <v>7.47603797912598</v>
+        <v>7.47603845596313</v>
       </c>
       <c r="H1154" t="n">
         <v>500</v>
@@ -33864,7 +33864,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1155" t="n">
-        <v>7.47603797912598</v>
+        <v>7.47603845596313</v>
       </c>
       <c r="H1155" t="n">
         <v>0</v>
@@ -33893,7 +33893,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1156" t="n">
-        <v>7.56296730041504</v>
+        <v>7.56296873092651</v>
       </c>
       <c r="H1156" t="n">
         <v>2000</v>
@@ -33922,7 +33922,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.99762058258057</v>
+        <v>7.99762105941772</v>
       </c>
       <c r="H1157" t="n">
         <v>24000</v>
@@ -33951,7 +33951,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.99762058258057</v>
+        <v>7.99762105941772</v>
       </c>
       <c r="H1158" t="n">
         <v>5000</v>
@@ -33980,7 +33980,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1159" t="n">
-        <v>8.51920700073242</v>
+        <v>8.51920604705811</v>
       </c>
       <c r="H1159" t="n">
         <v>38000</v>
@@ -34067,7 +34067,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1162" t="n">
-        <v>8.38880825042725</v>
+        <v>8.38880920410156</v>
       </c>
       <c r="H1162" t="n">
         <v>5000</v>
@@ -34154,7 +34154,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>8.30187797546387</v>
+        <v>8.30187892913818</v>
       </c>
       <c r="H1165" t="n">
         <v>8500</v>
@@ -34299,7 +34299,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.21494770050049</v>
+        <v>8.2149486541748</v>
       </c>
       <c r="H1170" t="n">
         <v>500</v>
@@ -34328,7 +34328,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.30187797546387</v>
+        <v>8.30187892913818</v>
       </c>
       <c r="H1171" t="n">
         <v>2500</v>
@@ -34357,7 +34357,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.43227577209473</v>
+        <v>8.43227481842041</v>
       </c>
       <c r="H1172" t="n">
         <v>2500</v>
@@ -34386,7 +34386,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1173" t="n">
-        <v>8.38880825042725</v>
+        <v>8.38880920410156</v>
       </c>
       <c r="H1173" t="n">
         <v>1000</v>
@@ -34415,7 +34415,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.38880825042725</v>
+        <v>8.38880920410156</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1175" t="n">
-        <v>8.21494770050049</v>
+        <v>8.2149486541748</v>
       </c>
       <c r="H1175" t="n">
         <v>6000</v>
@@ -34473,7 +34473,7 @@
         <v>9.5</v>
       </c>
       <c r="G1176" t="n">
-        <v>8.25841426849365</v>
+        <v>8.25841331481934</v>
       </c>
       <c r="H1176" t="n">
         <v>1500</v>
@@ -34502,7 +34502,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1177" t="n">
-        <v>8.38880825042725</v>
+        <v>8.38880920410156</v>
       </c>
       <c r="H1177" t="n">
         <v>500</v>
@@ -34531,7 +34531,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1178" t="n">
-        <v>8.51920700073242</v>
+        <v>8.51920604705811</v>
       </c>
       <c r="H1178" t="n">
         <v>4000</v>
@@ -34560,7 +34560,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1179" t="n">
-        <v>8.56267166137695</v>
+        <v>8.56267070770264</v>
       </c>
       <c r="H1179" t="n">
         <v>500</v>
@@ -34647,7 +34647,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1182" t="n">
-        <v>8.51920700073242</v>
+        <v>8.51920604705811</v>
       </c>
       <c r="H1182" t="n">
         <v>5000</v>
@@ -34676,7 +34676,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1183" t="n">
-        <v>8.60613632202148</v>
+        <v>8.6061372756958</v>
       </c>
       <c r="H1183" t="n">
         <v>4500</v>
@@ -34705,7 +34705,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.56267166137695</v>
+        <v>8.56267070770264</v>
       </c>
       <c r="H1184" t="n">
         <v>10000</v>
@@ -34821,7 +34821,7 @@
         <v>12</v>
       </c>
       <c r="G1188" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1188" t="n">
         <v>12500</v>
@@ -34850,7 +34850,7 @@
         <v>12</v>
       </c>
       <c r="G1189" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1189" t="n">
         <v>3500</v>
@@ -34879,7 +34879,7 @@
         <v>12</v>
       </c>
       <c r="G1190" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1190" t="n">
         <v>6000</v>
@@ -34908,7 +34908,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>10.7794036865234</v>
+        <v>10.7794027328491</v>
       </c>
       <c r="H1191" t="n">
         <v>4500</v>
@@ -34937,7 +34937,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1192" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1192" t="n">
         <v>2000</v>
@@ -34966,7 +34966,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>10.7794036865234</v>
+        <v>10.7794027328491</v>
       </c>
       <c r="H1193" t="n">
         <v>4000</v>
@@ -34995,7 +34995,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1194" t="n">
-        <v>10.7794036865234</v>
+        <v>10.7794027328491</v>
       </c>
       <c r="H1194" t="n">
         <v>6500</v>
@@ -35024,7 +35024,7 @@
         <v>12.5</v>
       </c>
       <c r="G1195" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1195" t="n">
         <v>3500</v>
@@ -35053,7 +35053,7 @@
         <v>12.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1196" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>12.5</v>
       </c>
       <c r="G1197" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1197" t="n">
         <v>0</v>
@@ -35111,7 +35111,7 @@
         <v>12.5</v>
       </c>
       <c r="G1198" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1198" t="n">
         <v>1000</v>
@@ -35140,7 +35140,7 @@
         <v>12.5</v>
       </c>
       <c r="G1199" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1199" t="n">
         <v>1500</v>
@@ -35169,7 +35169,7 @@
         <v>12.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1200" t="n">
         <v>500</v>
@@ -35256,7 +35256,7 @@
         <v>12.5</v>
       </c>
       <c r="G1203" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1203" t="n">
         <v>2500</v>
@@ -35285,7 +35285,7 @@
         <v>12.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1204" t="n">
         <v>0</v>
@@ -35314,7 +35314,7 @@
         <v>12.5</v>
       </c>
       <c r="G1205" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1205" t="n">
         <v>2000</v>
@@ -35343,7 +35343,7 @@
         <v>12.5</v>
       </c>
       <c r="G1206" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1206" t="n">
         <v>4500</v>
@@ -35372,7 +35372,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1207" t="n">
-        <v>11.0401945114136</v>
+        <v>11.0401954650879</v>
       </c>
       <c r="H1207" t="n">
         <v>1500</v>
@@ -35401,7 +35401,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>11.0401945114136</v>
+        <v>11.0401954650879</v>
       </c>
       <c r="H1208" t="n">
         <v>2000</v>
@@ -35430,7 +35430,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1209" t="n">
-        <v>11.0401945114136</v>
+        <v>11.0401954650879</v>
       </c>
       <c r="H1209" t="n">
         <v>0</v>
@@ -35459,7 +35459,7 @@
         <v>12.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1210" t="n">
         <v>500</v>
@@ -35662,7 +35662,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>10.7794036865234</v>
+        <v>10.7794027328491</v>
       </c>
       <c r="H1217" t="n">
         <v>500</v>
@@ -35691,7 +35691,7 @@
         <v>12</v>
       </c>
       <c r="G1218" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1218" t="n">
         <v>3000</v>
@@ -35749,7 +35749,7 @@
         <v>11.5</v>
       </c>
       <c r="G1220" t="n">
-        <v>9.99702739715576</v>
+        <v>9.99702644348145</v>
       </c>
       <c r="H1220" t="n">
         <v>7000</v>
@@ -35778,7 +35778,7 @@
         <v>11.5</v>
       </c>
       <c r="G1221" t="n">
-        <v>9.99702739715576</v>
+        <v>9.99702644348145</v>
       </c>
       <c r="H1221" t="n">
         <v>1500</v>
@@ -35836,7 +35836,7 @@
         <v>12.5</v>
       </c>
       <c r="G1223" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1223" t="n">
         <v>6000</v>
@@ -35894,7 +35894,7 @@
         <v>12.5</v>
       </c>
       <c r="G1225" t="n">
-        <v>10.8663339614868</v>
+        <v>10.8663330078125</v>
       </c>
       <c r="H1225" t="n">
         <v>1000</v>
@@ -35952,7 +35952,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1227" t="n">
-        <v>10.7794036865234</v>
+        <v>10.7794027328491</v>
       </c>
       <c r="H1227" t="n">
         <v>2500</v>
@@ -35981,7 +35981,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1228" t="n">
         <v>6000</v>
@@ -36010,7 +36010,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1229" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1229" t="n">
         <v>500</v>
@@ -36039,7 +36039,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1230" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1230" t="n">
         <v>500</v>
@@ -36068,7 +36068,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1231" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1231" t="n">
         <v>0</v>
@@ -36097,7 +36097,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1232" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1232" t="n">
         <v>0</v>
@@ -36126,7 +36126,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1233" t="n">
         <v>0</v>
@@ -36242,7 +36242,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1237" t="n">
         <v>500</v>
@@ -36271,7 +36271,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1238" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1238" t="n">
         <v>1500</v>
@@ -36300,7 +36300,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1239" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1239" t="n">
         <v>1500</v>
@@ -36329,7 +36329,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1240" t="n">
         <v>0</v>
@@ -36358,7 +36358,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1241" t="n">
         <v>0</v>
@@ -36387,7 +36387,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1242" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1242" t="n">
         <v>0</v>
@@ -36416,7 +36416,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1243" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1243" t="n">
         <v>0</v>
@@ -36445,7 +36445,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1244" t="n">
         <v>1500</v>
@@ -36474,7 +36474,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1245" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1245" t="n">
         <v>0</v>
@@ -36503,7 +36503,7 @@
         <v>12</v>
       </c>
       <c r="G1246" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1246" t="n">
         <v>500</v>
@@ -36532,7 +36532,7 @@
         <v>12</v>
       </c>
       <c r="G1247" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1247" t="n">
         <v>0</v>
@@ -36561,7 +36561,7 @@
         <v>12</v>
       </c>
       <c r="G1248" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1248" t="n">
         <v>0</v>
@@ -36590,7 +36590,7 @@
         <v>12</v>
       </c>
       <c r="G1249" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1249" t="n">
         <v>2000</v>
@@ -36619,7 +36619,7 @@
         <v>12</v>
       </c>
       <c r="G1250" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1250" t="n">
         <v>0</v>
@@ -36648,7 +36648,7 @@
         <v>12</v>
       </c>
       <c r="G1251" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1251" t="n">
         <v>500</v>
@@ -36677,7 +36677,7 @@
         <v>12</v>
       </c>
       <c r="G1252" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1252" t="n">
         <v>3500</v>
@@ -36706,7 +36706,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1253" t="n">
         <v>2000</v>
@@ -36735,7 +36735,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1254" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1254" t="n">
         <v>0</v>
@@ -36764,7 +36764,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1255" t="n">
         <v>0</v>
@@ -36793,7 +36793,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1256" t="n">
         <v>1500</v>
@@ -36822,7 +36822,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1257" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1257" t="n">
         <v>0</v>
@@ -36851,7 +36851,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1258" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1258" t="n">
         <v>500</v>
@@ -36880,7 +36880,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1259" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1259" t="n">
         <v>0</v>
@@ -36909,7 +36909,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1260" t="n">
         <v>0</v>
@@ -36938,7 +36938,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1261" t="n">
-        <v>10.1708879470825</v>
+        <v>10.1708889007568</v>
       </c>
       <c r="H1261" t="n">
         <v>2500</v>
@@ -36996,7 +36996,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.1708879470825</v>
+        <v>10.1708889007568</v>
       </c>
       <c r="H1263" t="n">
         <v>6500</v>
@@ -37025,7 +37025,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.1708879470825</v>
+        <v>10.1708889007568</v>
       </c>
       <c r="H1264" t="n">
         <v>0</v>
@@ -37054,7 +37054,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.1708879470825</v>
+        <v>10.1708889007568</v>
       </c>
       <c r="H1265" t="n">
         <v>0</v>
@@ -37112,7 +37112,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1267" t="n">
         <v>1000</v>
@@ -37141,7 +37141,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1268" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1268" t="n">
         <v>0</v>
@@ -37257,7 +37257,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1272" t="n">
-        <v>9.73623466491699</v>
+        <v>9.73623371124268</v>
       </c>
       <c r="H1272" t="n">
         <v>1000</v>
@@ -37286,7 +37286,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1273" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1273" t="n">
         <v>2000</v>
@@ -37315,7 +37315,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1274" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1274" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1275" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1275" t="n">
         <v>0</v>
@@ -37373,7 +37373,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1276" t="n">
         <v>1000</v>
@@ -37402,7 +37402,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1277" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1277" t="n">
         <v>0</v>
@@ -37431,7 +37431,7 @@
         <v>11.5</v>
       </c>
       <c r="G1278" t="n">
-        <v>9.99702739715576</v>
+        <v>9.99702644348145</v>
       </c>
       <c r="H1278" t="n">
         <v>2500</v>
@@ -37489,7 +37489,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1280" t="n">
         <v>3000</v>
@@ -37518,7 +37518,7 @@
         <v>11.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>9.99702739715576</v>
+        <v>9.99702644348145</v>
       </c>
       <c r="H1281" t="n">
         <v>500</v>
@@ -37547,7 +37547,7 @@
         <v>11.5</v>
       </c>
       <c r="G1282" t="n">
-        <v>9.99702739715576</v>
+        <v>9.99702644348145</v>
       </c>
       <c r="H1282" t="n">
         <v>0</v>
@@ -37576,7 +37576,7 @@
         <v>11.5</v>
       </c>
       <c r="G1283" t="n">
-        <v>9.99702739715576</v>
+        <v>9.99702644348145</v>
       </c>
       <c r="H1283" t="n">
         <v>0</v>
@@ -37605,7 +37605,7 @@
         <v>11.5</v>
       </c>
       <c r="G1284" t="n">
-        <v>9.99702739715576</v>
+        <v>9.99702644348145</v>
       </c>
       <c r="H1284" t="n">
         <v>0</v>
@@ -37634,7 +37634,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1285" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1285" t="n">
         <v>71000</v>
@@ -37663,7 +37663,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1286" t="n">
-        <v>10.1708879470825</v>
+        <v>10.1708889007568</v>
       </c>
       <c r="H1286" t="n">
         <v>1500</v>
@@ -37692,7 +37692,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1287" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1287" t="n">
         <v>1500</v>
@@ -37750,7 +37750,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1289" t="n">
-        <v>9.91009521484375</v>
+        <v>9.91009616851807</v>
       </c>
       <c r="H1289" t="n">
         <v>4500</v>
@@ -37779,7 +37779,7 @@
         <v>11.5</v>
       </c>
       <c r="G1290" t="n">
-        <v>9.99702739715576</v>
+        <v>9.99702644348145</v>
       </c>
       <c r="H1290" t="n">
         <v>3500</v>
@@ -37866,7 +37866,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1293" t="n">
-        <v>10.3447484970093</v>
+        <v>10.3447494506836</v>
       </c>
       <c r="H1293" t="n">
         <v>1000</v>
@@ -37895,7 +37895,7 @@
         <v>12</v>
       </c>
       <c r="G1294" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1294" t="n">
         <v>1000</v>
@@ -37953,7 +37953,7 @@
         <v>12</v>
       </c>
       <c r="G1296" t="n">
-        <v>10.431679725647</v>
+        <v>10.4316806793213</v>
       </c>
       <c r="H1296" t="n">
         <v>1000</v>
@@ -37982,7 +37982,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1297" t="n">
-        <v>10.605541229248</v>
+        <v>10.6055421829224</v>
       </c>
       <c r="H1297" t="n">
         <v>1000</v>
@@ -38098,7 +38098,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>12.2572240829468</v>
+        <v>12.2572250366211</v>
       </c>
       <c r="H1301" t="n">
         <v>11500</v>
@@ -38127,7 +38127,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1302" t="n">
-        <v>12.2572240829468</v>
+        <v>12.2572250366211</v>
       </c>
       <c r="H1302" t="n">
         <v>7500</v>
@@ -38243,7 +38243,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1306" t="n">
-        <v>13.1265325546265</v>
+        <v>13.1265316009521</v>
       </c>
       <c r="H1306" t="n">
         <v>7000</v>
@@ -38301,7 +38301,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1308" t="n">
-        <v>12.6918783187866</v>
+        <v>12.6918773651123</v>
       </c>
       <c r="H1308" t="n">
         <v>4250</v>
@@ -38388,7 +38388,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1311" t="n">
-        <v>13.1265325546265</v>
+        <v>13.1265316009521</v>
       </c>
       <c r="H1311" t="n">
         <v>10250</v>
@@ -38475,7 +38475,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1314" t="n">
-        <v>12.5180168151855</v>
+        <v>12.5180158615112</v>
       </c>
       <c r="H1314" t="n">
         <v>4000</v>
@@ -38504,7 +38504,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1315" t="n">
-        <v>12.5180168151855</v>
+        <v>12.5180158615112</v>
       </c>
       <c r="H1315" t="n">
         <v>0</v>
@@ -38562,7 +38562,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1317" t="n">
-        <v>12.3441553115845</v>
+        <v>12.3441543579102</v>
       </c>
       <c r="H1317" t="n">
         <v>1500</v>
@@ -38591,7 +38591,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>12.6918783187866</v>
+        <v>12.6918773651123</v>
       </c>
       <c r="H1318" t="n">
         <v>500</v>
@@ -38620,7 +38620,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1319" t="n">
-        <v>12.6918783187866</v>
+        <v>12.6918773651123</v>
       </c>
       <c r="H1319" t="n">
         <v>250</v>
@@ -38649,7 +38649,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>12.6918783187866</v>
+        <v>12.6918773651123</v>
       </c>
       <c r="H1320" t="n">
         <v>500</v>
@@ -38707,7 +38707,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>12.5180168151855</v>
+        <v>12.5180158615112</v>
       </c>
       <c r="H1322" t="n">
         <v>1500</v>
@@ -38765,7 +38765,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1324" t="n">
-        <v>12.77880859375</v>
+        <v>12.7788066864014</v>
       </c>
       <c r="H1324" t="n">
         <v>750</v>
@@ -38910,7 +38910,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1329" t="n">
-        <v>12.6918783187866</v>
+        <v>12.6918773651123</v>
       </c>
       <c r="H1329" t="n">
         <v>250</v>
@@ -38968,7 +38968,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>12.5180168151855</v>
+        <v>12.5180158615112</v>
       </c>
       <c r="H1331" t="n">
         <v>250</v>
@@ -38997,7 +38997,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1332" t="n">
-        <v>12.77880859375</v>
+        <v>12.7788066864014</v>
       </c>
       <c r="H1332" t="n">
         <v>1250</v>
@@ -39055,7 +39055,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1334" t="n">
-        <v>12.5180168151855</v>
+        <v>12.5180158615112</v>
       </c>
       <c r="H1334" t="n">
         <v>1000</v>
@@ -39142,7 +39142,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>12.77880859375</v>
+        <v>12.7788066864014</v>
       </c>
       <c r="H1337" t="n">
         <v>3500</v>
@@ -39200,7 +39200,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1339" t="n">
-        <v>12.77880859375</v>
+        <v>12.7788066864014</v>
       </c>
       <c r="H1339" t="n">
         <v>500</v>
@@ -39374,7 +39374,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1345" t="n">
-        <v>13.1265325546265</v>
+        <v>13.1265316009521</v>
       </c>
       <c r="H1345" t="n">
         <v>11000</v>
@@ -39577,7 +39577,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1352" t="n">
-        <v>13.1265325546265</v>
+        <v>13.1265316009521</v>
       </c>
       <c r="H1352" t="n">
         <v>1250</v>
@@ -39693,7 +39693,7 @@
         <v>15.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>13.47425365448</v>
+        <v>13.4742527008057</v>
       </c>
       <c r="H1356" t="n">
         <v>2250</v>
@@ -39722,7 +39722,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.1265325546265</v>
+        <v>13.1265316009521</v>
       </c>
       <c r="H1357" t="n">
         <v>9250</v>
@@ -39809,7 +39809,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1360" t="n">
-        <v>13.1265325546265</v>
+        <v>13.1265316009521</v>
       </c>
       <c r="H1360" t="n">
         <v>3250</v>
@@ -39838,7 +39838,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.1265325546265</v>
+        <v>13.1265316009521</v>
       </c>
       <c r="H1361" t="n">
         <v>0</v>
@@ -39867,7 +39867,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1362" t="n">
-        <v>13.1265325546265</v>
+        <v>13.1265316009521</v>
       </c>
       <c r="H1362" t="n">
         <v>0</v>
@@ -39896,7 +39896,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1363" t="n">
-        <v>13.1265325546265</v>
+        <v>13.1265316009521</v>
       </c>
       <c r="H1363" t="n">
         <v>1000</v>
@@ -39925,7 +39925,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1364" t="n">
-        <v>13.9958372116089</v>
+        <v>13.9958391189575</v>
       </c>
       <c r="H1364" t="n">
         <v>8250</v>
@@ -39954,7 +39954,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>13.9958372116089</v>
+        <v>13.9958391189575</v>
       </c>
       <c r="H1365" t="n">
         <v>5250</v>
@@ -39983,7 +39983,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1366" t="n">
-        <v>14.8651447296143</v>
+        <v>14.8651466369629</v>
       </c>
       <c r="H1366" t="n">
         <v>1750</v>
@@ -40070,7 +40070,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1369" t="n">
-        <v>14.1696977615356</v>
+        <v>14.16969871521</v>
       </c>
       <c r="H1369" t="n">
         <v>750</v>
@@ -40099,7 +40099,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>14.1696977615356</v>
+        <v>14.16969871521</v>
       </c>
       <c r="H1370" t="n">
         <v>0</v>
@@ -40128,7 +40128,7 @@
         <v>16.5</v>
       </c>
       <c r="G1371" t="n">
-        <v>14.3435611724854</v>
+        <v>14.343560218811</v>
       </c>
       <c r="H1371" t="n">
         <v>250</v>
@@ -40157,7 +40157,7 @@
         <v>16.5</v>
       </c>
       <c r="G1372" t="n">
-        <v>14.3435611724854</v>
+        <v>14.343560218811</v>
       </c>
       <c r="H1372" t="n">
         <v>0</v>
@@ -40186,7 +40186,7 @@
         <v>16.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>14.3435611724854</v>
+        <v>14.343560218811</v>
       </c>
       <c r="H1373" t="n">
         <v>0</v>
@@ -40215,7 +40215,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1374" t="n">
-        <v>14.0827684402466</v>
+        <v>14.0827693939209</v>
       </c>
       <c r="H1374" t="n">
         <v>2500</v>
@@ -40244,7 +40244,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1375" t="n">
-        <v>13.9958372116089</v>
+        <v>13.9958391189575</v>
       </c>
       <c r="H1375" t="n">
         <v>250</v>
@@ -40447,7 +40447,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1382" t="n">
-        <v>13.7722606658936</v>
+        <v>13.7722616195679</v>
       </c>
       <c r="H1382" t="n">
         <v>1500</v>
@@ -40476,7 +40476,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1383" t="n">
-        <v>13.7722606658936</v>
+        <v>13.7722616195679</v>
       </c>
       <c r="H1383" t="n">
         <v>0</v>
@@ -40505,7 +40505,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="n">
-        <v>14.3982734680176</v>
+        <v>14.3982744216919</v>
       </c>
       <c r="H1384" t="n">
         <v>500</v>
@@ -40621,7 +40621,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1388" t="n">
-        <v>14.2194137573242</v>
+        <v>14.2194128036499</v>
       </c>
       <c r="H1388" t="n">
         <v>250</v>
@@ -40650,7 +40650,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1389" t="n">
-        <v>14.2194137573242</v>
+        <v>14.2194128036499</v>
       </c>
       <c r="H1389" t="n">
         <v>0</v>
@@ -40679,7 +40679,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>14.2194137573242</v>
+        <v>14.2194128036499</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1391" t="n">
-        <v>14.2194137573242</v>
+        <v>14.2194128036499</v>
       </c>
       <c r="H1391" t="n">
         <v>0</v>
@@ -40737,7 +40737,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1392" t="n">
-        <v>14.2194137573242</v>
+        <v>14.2194128036499</v>
       </c>
       <c r="H1392" t="n">
         <v>0</v>
@@ -40766,7 +40766,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1393" t="n">
-        <v>14.2194137573242</v>
+        <v>14.2194128036499</v>
       </c>
       <c r="H1393" t="n">
         <v>0</v>
@@ -40795,7 +40795,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1394" t="n">
-        <v>14.2194137573242</v>
+        <v>14.2194128036499</v>
       </c>
       <c r="H1394" t="n">
         <v>0</v>
@@ -40998,7 +40998,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1401" t="n">
-        <v>14.3982734680176</v>
+        <v>14.3982744216919</v>
       </c>
       <c r="H1401" t="n">
         <v>2000</v>
@@ -41027,7 +41027,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>14.9348554611206</v>
+        <v>14.9348564147949</v>
       </c>
       <c r="H1402" t="n">
         <v>3750</v>
@@ -41056,7 +41056,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>15.1137170791626</v>
+        <v>15.1137161254883</v>
       </c>
       <c r="H1403" t="n">
         <v>1500</v>
@@ -41085,7 +41085,7 @@
         <v>17.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>15.6502981185913</v>
+        <v>15.6502962112427</v>
       </c>
       <c r="H1404" t="n">
         <v>1500</v>
@@ -41114,7 +41114,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1405" t="n">
-        <v>15.9185876846313</v>
+        <v>15.918586730957</v>
       </c>
       <c r="H1405" t="n">
         <v>1500</v>
@@ -41172,7 +41172,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1407" t="n">
-        <v>15.1137170791626</v>
+        <v>15.1137161254883</v>
       </c>
       <c r="H1407" t="n">
         <v>4500</v>
@@ -41201,7 +41201,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>15.1137170791626</v>
+        <v>15.1137161254883</v>
       </c>
       <c r="H1408" t="n">
         <v>5000</v>
@@ -41230,7 +41230,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.1137170791626</v>
+        <v>15.1137161254883</v>
       </c>
       <c r="H1409" t="n">
         <v>0</v>
@@ -41288,7 +41288,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>16.7234630584717</v>
+        <v>16.723461151123</v>
       </c>
       <c r="H1411" t="n">
         <v>1250</v>
@@ -41375,7 +41375,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1414" t="n">
-        <v>17.0811805725098</v>
+        <v>17.0811824798584</v>
       </c>
       <c r="H1414" t="n">
         <v>1500</v>
@@ -41404,7 +41404,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1415" t="n">
-        <v>17.0811805725098</v>
+        <v>17.0811824798584</v>
       </c>
       <c r="H1415" t="n">
         <v>0</v>
@@ -41607,7 +41607,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1422" t="n">
-        <v>22.7152881622314</v>
+        <v>22.7152900695801</v>
       </c>
       <c r="H1422" t="n">
         <v>2500</v>
@@ -41665,7 +41665,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1424" t="n">
-        <v>22.7152881622314</v>
+        <v>22.7152900695801</v>
       </c>
       <c r="H1424" t="n">
         <v>6250</v>
@@ -41694,7 +41694,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1425" t="n">
-        <v>22.1787090301514</v>
+        <v>22.1787071228027</v>
       </c>
       <c r="H1425" t="n">
         <v>3500</v>
@@ -41810,7 +41810,7 @@
         <v>21</v>
       </c>
       <c r="G1429" t="n">
-        <v>18.7803573608398</v>
+        <v>18.7803592681885</v>
       </c>
       <c r="H1429" t="n">
         <v>1250</v>
@@ -41868,7 +41868,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>22.1787090301514</v>
+        <v>22.1787071228027</v>
       </c>
       <c r="H1431" t="n">
         <v>2000</v>
@@ -41984,7 +41984,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>22.1787090301514</v>
+        <v>22.1787071228027</v>
       </c>
       <c r="H1435" t="n">
         <v>750</v>
@@ -42013,7 +42013,7 @@
         <v>25</v>
       </c>
       <c r="G1436" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1436" t="n">
         <v>2000</v>
@@ -42042,7 +42042,7 @@
         <v>25</v>
       </c>
       <c r="G1437" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1437" t="n">
         <v>250</v>
@@ -42100,7 +42100,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>23.0730094909668</v>
+        <v>23.0730075836182</v>
       </c>
       <c r="H1439" t="n">
         <v>750</v>
@@ -42129,7 +42129,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>22.7152881622314</v>
+        <v>22.7152900695801</v>
       </c>
       <c r="H1440" t="n">
         <v>1250</v>
@@ -42158,7 +42158,7 @@
         <v>25</v>
       </c>
       <c r="G1441" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1441" t="n">
         <v>1000</v>
@@ -42187,7 +42187,7 @@
         <v>25</v>
       </c>
       <c r="G1442" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1442" t="n">
         <v>0</v>
@@ -42216,7 +42216,7 @@
         <v>25</v>
       </c>
       <c r="G1443" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1443" t="n">
         <v>0</v>
@@ -42245,7 +42245,7 @@
         <v>25</v>
       </c>
       <c r="G1444" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1444" t="n">
         <v>0</v>
@@ -42274,7 +42274,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1445" t="n">
-        <v>22.7152881622314</v>
+        <v>22.7152900695801</v>
       </c>
       <c r="H1445" t="n">
         <v>1000</v>
@@ -42303,7 +42303,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>22.7152881622314</v>
+        <v>22.7152900695801</v>
       </c>
       <c r="H1446" t="n">
         <v>1250</v>
@@ -42767,7 +42767,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>23.0730094909668</v>
+        <v>23.0730075836182</v>
       </c>
       <c r="H1462" t="n">
         <v>500</v>
@@ -42825,7 +42825,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1464" t="n">
-        <v>22.7152881622314</v>
+        <v>22.7152900695801</v>
       </c>
       <c r="H1464" t="n">
         <v>1750</v>
@@ -42912,7 +42912,7 @@
         <v>25</v>
       </c>
       <c r="G1467" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1467" t="n">
         <v>500</v>
@@ -42941,7 +42941,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1468" t="n">
-        <v>22.7152881622314</v>
+        <v>22.7152900695801</v>
       </c>
       <c r="H1468" t="n">
         <v>750</v>
@@ -42970,7 +42970,7 @@
         <v>25</v>
       </c>
       <c r="G1469" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1469" t="n">
         <v>500</v>
@@ -43028,7 +43028,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>22.7152881622314</v>
+        <v>22.7152900695801</v>
       </c>
       <c r="H1471" t="n">
         <v>250</v>
@@ -43057,7 +43057,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1472" t="n">
-        <v>22.7152881622314</v>
+        <v>22.7152900695801</v>
       </c>
       <c r="H1472" t="n">
         <v>0</v>
@@ -43376,7 +43376,7 @@
         <v>25</v>
       </c>
       <c r="G1483" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1483" t="n">
         <v>1000</v>
@@ -43405,7 +43405,7 @@
         <v>25</v>
       </c>
       <c r="G1484" t="n">
-        <v>22.3575687408447</v>
+        <v>22.3575668334961</v>
       </c>
       <c r="H1484" t="n">
         <v>0</v>
@@ -43434,7 +43434,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1485" t="n">
-        <v>21.8209857940674</v>
+        <v>21.820987701416</v>
       </c>
       <c r="H1485" t="n">
         <v>1000</v>
@@ -43463,7 +43463,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1486" t="n">
-        <v>21.8209857940674</v>
+        <v>21.820987701416</v>
       </c>
       <c r="H1486" t="n">
         <v>0</v>
@@ -43724,7 +43724,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1495" t="n">
-        <v>25.2193355560303</v>
+        <v>25.2193374633789</v>
       </c>
       <c r="H1495" t="n">
         <v>2250</v>
@@ -43811,7 +43811,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1498" t="n">
-        <v>30.0485687255859</v>
+        <v>30.0485668182373</v>
       </c>
       <c r="H1498" t="n">
         <v>2500</v>
@@ -43869,7 +43869,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1500" t="n">
-        <v>29.8697109222412</v>
+        <v>29.8697128295898</v>
       </c>
       <c r="H1500" t="n">
         <v>1500</v>
@@ -43898,7 +43898,7 @@
         <v>33</v>
       </c>
       <c r="G1501" t="n">
-        <v>29.5119915008545</v>
+        <v>29.5119895935059</v>
       </c>
       <c r="H1501" t="n">
         <v>6000</v>
@@ -43927,7 +43927,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>28.4388275146484</v>
+        <v>28.4388256072998</v>
       </c>
       <c r="H1502" t="n">
         <v>3250</v>
@@ -43956,7 +43956,7 @@
         <v>33</v>
       </c>
       <c r="G1503" t="n">
-        <v>29.5119915008545</v>
+        <v>29.5119895935059</v>
       </c>
       <c r="H1503" t="n">
         <v>500</v>
@@ -43985,7 +43985,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>30.0485687255859</v>
+        <v>30.0485668182373</v>
       </c>
       <c r="H1504" t="n">
         <v>1750</v>
@@ -44014,7 +44014,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1505" t="n">
-        <v>30.5851535797119</v>
+        <v>30.5851554870605</v>
       </c>
       <c r="H1505" t="n">
         <v>4750</v>
@@ -44130,7 +44130,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1509" t="n">
-        <v>32.9103355407715</v>
+        <v>32.9103393554688</v>
       </c>
       <c r="H1509" t="n">
         <v>4750</v>
@@ -44188,7 +44188,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1511" t="n">
-        <v>29.3331279754639</v>
+        <v>29.3331260681152</v>
       </c>
       <c r="H1511" t="n">
         <v>8000</v>
@@ -44304,7 +44304,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1515" t="n">
-        <v>24.8616142272949</v>
+        <v>24.8616161346436</v>
       </c>
       <c r="H1515" t="n">
         <v>3250</v>
@@ -44478,7 +44478,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>27.0079441070557</v>
+        <v>27.007942199707</v>
       </c>
       <c r="H1521" t="n">
         <v>2250</v>
@@ -44565,7 +44565,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1524" t="n">
-        <v>28.4388275146484</v>
+        <v>28.4388256072998</v>
       </c>
       <c r="H1524" t="n">
         <v>1750</v>
@@ -44768,7 +44768,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>27.5445213317871</v>
+        <v>27.5445232391357</v>
       </c>
       <c r="H1531" t="n">
         <v>500</v>
@@ -44797,7 +44797,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1532" t="n">
-        <v>27.5445213317871</v>
+        <v>27.5445232391357</v>
       </c>
       <c r="H1532" t="n">
         <v>0</v>
@@ -44826,7 +44826,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1533" t="n">
-        <v>26.2924995422363</v>
+        <v>26.2924976348877</v>
       </c>
       <c r="H1533" t="n">
         <v>1000</v>
@@ -44884,7 +44884,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1535" t="n">
-        <v>26.2924995422363</v>
+        <v>26.2924976348877</v>
       </c>
       <c r="H1535" t="n">
         <v>250</v>
@@ -44913,7 +44913,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1536" t="n">
-        <v>26.2924995422363</v>
+        <v>26.2924976348877</v>
       </c>
       <c r="H1536" t="n">
         <v>250</v>
@@ -44942,7 +44942,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1537" t="n">
-        <v>26.2924995422363</v>
+        <v>26.2924976348877</v>
       </c>
       <c r="H1537" t="n">
         <v>0</v>
@@ -44971,7 +44971,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1538" t="n">
-        <v>26.2924995422363</v>
+        <v>26.2924976348877</v>
       </c>
       <c r="H1538" t="n">
         <v>0</v>
@@ -45000,7 +45000,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1539" t="n">
-        <v>26.2924995422363</v>
+        <v>26.2924976348877</v>
       </c>
       <c r="H1539" t="n">
         <v>0</v>
@@ -45029,7 +45029,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.2924995422363</v>
+        <v>26.2924976348877</v>
       </c>
       <c r="H1540" t="n">
         <v>0</v>
@@ -45058,7 +45058,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1541" t="n">
-        <v>24.6827564239502</v>
+        <v>24.6827545166016</v>
       </c>
       <c r="H1541" t="n">
         <v>2250</v>
@@ -45116,7 +45116,7 @@
         <v>28</v>
       </c>
       <c r="G1543" t="n">
-        <v>25.0404758453369</v>
+        <v>25.0404777526855</v>
       </c>
       <c r="H1543" t="n">
         <v>750</v>
@@ -45145,7 +45145,7 @@
         <v>28</v>
       </c>
       <c r="G1544" t="n">
-        <v>25.0404758453369</v>
+        <v>25.0404777526855</v>
       </c>
       <c r="H1544" t="n">
         <v>5250</v>
@@ -45174,7 +45174,7 @@
         <v>28</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.0404758453369</v>
+        <v>25.0404777526855</v>
       </c>
       <c r="H1545" t="n">
         <v>0</v>
@@ -45203,7 +45203,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1546" t="n">
-        <v>24.6827564239502</v>
+        <v>24.6827545166016</v>
       </c>
       <c r="H1546" t="n">
         <v>500</v>
@@ -45232,7 +45232,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.6827564239502</v>
+        <v>24.6827545166016</v>
       </c>
       <c r="H1547" t="n">
         <v>10000</v>
@@ -45261,7 +45261,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>24.6827564239502</v>
+        <v>24.6827545166016</v>
       </c>
       <c r="H1548" t="n">
         <v>0</v>
@@ -45319,7 +45319,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.2193355560303</v>
+        <v>25.2193374633789</v>
       </c>
       <c r="H1550" t="n">
         <v>1750</v>
@@ -45348,7 +45348,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1551" t="n">
-        <v>25.2193355560303</v>
+        <v>25.2193374633789</v>
       </c>
       <c r="H1551" t="n">
         <v>0</v>
@@ -45986,7 +45986,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1573" t="n">
-        <v>30.0485687255859</v>
+        <v>30.0485668182373</v>
       </c>
       <c r="H1573" t="n">
         <v>4750</v>
@@ -46015,7 +46015,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1574" t="n">
-        <v>29.3331279754639</v>
+        <v>29.3331260681152</v>
       </c>
       <c r="H1574" t="n">
         <v>5000</v>
@@ -46044,7 +46044,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1575" t="n">
-        <v>29.3331279754639</v>
+        <v>29.3331260681152</v>
       </c>
       <c r="H1575" t="n">
         <v>0</v>
@@ -46073,7 +46073,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1576" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1576" t="n">
         <v>1000</v>
@@ -46131,7 +46131,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1578" t="n">
-        <v>28.4388275146484</v>
+        <v>28.4388256072998</v>
       </c>
       <c r="H1578" t="n">
         <v>1500</v>
@@ -46160,7 +46160,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1579" t="n">
-        <v>28.7965469360352</v>
+        <v>28.7965488433838</v>
       </c>
       <c r="H1579" t="n">
         <v>500</v>
@@ -46247,7 +46247,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1582" t="n">
-        <v>27.5445213317871</v>
+        <v>27.5445232391357</v>
       </c>
       <c r="H1582" t="n">
         <v>500</v>
@@ -46334,7 +46334,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1585" t="n">
-        <v>29.8697109222412</v>
+        <v>29.8697128295898</v>
       </c>
       <c r="H1585" t="n">
         <v>4750</v>
@@ -46363,7 +46363,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1586" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1586" t="n">
         <v>1000</v>
@@ -46479,7 +46479,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1590" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1590" t="n">
         <v>2750</v>
@@ -46508,7 +46508,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1591" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1591" t="n">
         <v>0</v>
@@ -46537,7 +46537,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1592" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1592" t="n">
         <v>0</v>
@@ -46566,7 +46566,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1593" t="n">
-        <v>30.5851535797119</v>
+        <v>30.5851554870605</v>
       </c>
       <c r="H1593" t="n">
         <v>1500</v>
@@ -46595,7 +46595,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1594" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1594" t="n">
         <v>750</v>
@@ -46653,7 +46653,7 @@
         <v>33</v>
       </c>
       <c r="G1596" t="n">
-        <v>29.5119915008545</v>
+        <v>29.5119895935059</v>
       </c>
       <c r="H1596" t="n">
         <v>1500</v>
@@ -46682,7 +46682,7 @@
         <v>33</v>
       </c>
       <c r="G1597" t="n">
-        <v>29.5119915008545</v>
+        <v>29.5119895935059</v>
       </c>
       <c r="H1597" t="n">
         <v>250</v>
@@ -46711,7 +46711,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1598" t="n">
-        <v>28.4388275146484</v>
+        <v>28.4388256072998</v>
       </c>
       <c r="H1598" t="n">
         <v>500</v>
@@ -46740,7 +46740,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1599" t="n">
-        <v>28.7965469360352</v>
+        <v>28.7965488433838</v>
       </c>
       <c r="H1599" t="n">
         <v>500</v>
@@ -46885,7 +46885,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1604" t="n">
-        <v>28.4388275146484</v>
+        <v>28.4388256072998</v>
       </c>
       <c r="H1604" t="n">
         <v>750</v>
@@ -46914,7 +46914,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1605" t="n">
-        <v>28.4388275146484</v>
+        <v>28.4388256072998</v>
       </c>
       <c r="H1605" t="n">
         <v>250</v>
@@ -46943,7 +46943,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1606" t="n">
-        <v>28.4388275146484</v>
+        <v>28.4388256072998</v>
       </c>
       <c r="H1606" t="n">
         <v>0</v>
@@ -46972,7 +46972,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1607" t="n">
-        <v>27.5445213317871</v>
+        <v>27.5445232391357</v>
       </c>
       <c r="H1607" t="n">
         <v>250</v>
@@ -47088,7 +47088,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1611" t="n">
-        <v>29.8697109222412</v>
+        <v>29.8697128295898</v>
       </c>
       <c r="H1611" t="n">
         <v>2000</v>
@@ -47117,7 +47117,7 @@
         <v>35</v>
       </c>
       <c r="G1612" t="n">
-        <v>31.3005962371826</v>
+        <v>31.3005924224854</v>
       </c>
       <c r="H1612" t="n">
         <v>1250</v>
@@ -47146,7 +47146,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1613" t="n">
         <v>3250</v>
@@ -47175,7 +47175,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1614" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1614" t="n">
         <v>0</v>
@@ -47204,7 +47204,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1615" t="n">
-        <v>30.0485687255859</v>
+        <v>30.0485668182373</v>
       </c>
       <c r="H1615" t="n">
         <v>250</v>
@@ -47233,7 +47233,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1616" t="n">
-        <v>30.0485687255859</v>
+        <v>30.0485668182373</v>
       </c>
       <c r="H1616" t="n">
         <v>0</v>
@@ -47262,7 +47262,7 @@
         <v>33</v>
       </c>
       <c r="G1617" t="n">
-        <v>29.5119915008545</v>
+        <v>29.5119895935059</v>
       </c>
       <c r="H1617" t="n">
         <v>1250</v>
@@ -47378,7 +47378,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1621" t="n">
-        <v>30.7640151977539</v>
+        <v>30.7640171051025</v>
       </c>
       <c r="H1621" t="n">
         <v>1500</v>
@@ -47407,7 +47407,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1622" t="n">
-        <v>30.7640151977539</v>
+        <v>30.7640171051025</v>
       </c>
       <c r="H1622" t="n">
         <v>0</v>
@@ -47436,7 +47436,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1623" t="n">
-        <v>30.7640151977539</v>
+        <v>30.7640171051025</v>
       </c>
       <c r="H1623" t="n">
         <v>0</v>
@@ -47465,7 +47465,7 @@
         <v>33</v>
       </c>
       <c r="G1624" t="n">
-        <v>29.5119915008545</v>
+        <v>29.5119895935059</v>
       </c>
       <c r="H1624" t="n">
         <v>500</v>
@@ -47494,7 +47494,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1625" t="n">
-        <v>31.1217308044434</v>
+        <v>31.1217346191406</v>
       </c>
       <c r="H1625" t="n">
         <v>51750</v>
@@ -47610,7 +47610,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1629" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1629" t="n">
         <v>250</v>
@@ -47639,7 +47639,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1630" t="n">
         <v>250</v>
@@ -47668,7 +47668,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1631" t="n">
         <v>0</v>
@@ -47697,7 +47697,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1632" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1632" t="n">
         <v>0</v>
@@ -47726,7 +47726,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1633" t="n">
-        <v>29.6908512115479</v>
+        <v>29.6908493041992</v>
       </c>
       <c r="H1633" t="n">
         <v>0</v>
@@ -47784,7 +47784,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1635" t="n">
-        <v>30.7640151977539</v>
+        <v>30.7640171051025</v>
       </c>
       <c r="H1635" t="n">
         <v>2250</v>
